--- a/server/scripts/multi data/Faculty_Template_Updated_multi.xlsx
+++ b/server/scripts/multi data/Faculty_Template_Updated_multi.xlsx
@@ -37,7 +37,7 @@
     <t>role</t>
   </si>
   <si>
-    <t>(multi)50007</t>
+    <t>(MULTI)50007</t>
   </si>
   <si>
     <t>SIVAGAMI   M</t>
@@ -55,7 +55,7 @@
     <t>faculty</t>
   </si>
   <si>
-    <t>(multi)50011</t>
+    <t>(MULTI)50011</t>
   </si>
   <si>
     <t>SABUMON P C</t>
@@ -67,7 +67,7 @@
     <t>Vit50011@123</t>
   </si>
   <si>
-    <t>(multi)50030</t>
+    <t>(MULTI)50030</t>
   </si>
   <si>
     <t>BRINTHA THERESE  A</t>
@@ -79,7 +79,7 @@
     <t>Vit50030@123</t>
   </si>
   <si>
-    <t>(multi)50038</t>
+    <t>(MULTI)50038</t>
   </si>
   <si>
     <t>SRIMATHI  R</t>
@@ -91,7 +91,7 @@
     <t>Vit50038@123</t>
   </si>
   <si>
-    <t>(multi)50046</t>
+    <t>(MULTI)50046</t>
   </si>
   <si>
     <t>JOHN KENNEDY  L</t>
@@ -103,7 +103,7 @@
     <t>Vit50046@123</t>
   </si>
   <si>
-    <t>(multi)50050</t>
+    <t>(MULTI)50050</t>
   </si>
   <si>
     <t>ATANU DUTTA</t>
@@ -115,7 +115,7 @@
     <t>Vit50050@123</t>
   </si>
   <si>
-    <t>(multi)50063</t>
+    <t>(MULTI)50063</t>
   </si>
   <si>
     <t>S.A.SAJIDHA</t>
@@ -127,7 +127,7 @@
     <t>Vit50063@123</t>
   </si>
   <si>
-    <t>(multi)50066</t>
+    <t>(MULTI)50066</t>
   </si>
   <si>
     <t>REVATHI S</t>
@@ -139,7 +139,7 @@
     <t>Vit50066@123</t>
   </si>
   <si>
-    <t>(multi)50067</t>
+    <t>(MULTI)50067</t>
   </si>
   <si>
     <t>AUGUSTA SOPHY BEULET P</t>
@@ -151,7 +151,7 @@
     <t>Vit50067@123</t>
   </si>
   <si>
-    <t>(multi)50078</t>
+    <t>(MULTI)50078</t>
   </si>
   <si>
     <t>SUBHASHINI N</t>
@@ -163,7 +163,7 @@
     <t>Vit50078@123</t>
   </si>
   <si>
-    <t>(multi)50083</t>
+    <t>(MULTI)50083</t>
   </si>
   <si>
     <t>SREEDEVI V T</t>
@@ -175,7 +175,7 @@
     <t>Vit50083@123</t>
   </si>
   <si>
-    <t>(multi)50094</t>
+    <t>(MULTI)50094</t>
   </si>
   <si>
     <t>JEGANNATHAN L</t>
@@ -187,7 +187,7 @@
     <t>Vit50094@123</t>
   </si>
   <si>
-    <t>(multi)50103</t>
+    <t>(MULTI)50103</t>
   </si>
   <si>
     <t>KALIYAPPAN M</t>
@@ -199,7 +199,7 @@
     <t>Vit50103@123</t>
   </si>
   <si>
-    <t>(multi)50125</t>
+    <t>(MULTI)50125</t>
   </si>
   <si>
     <t>MINI GHOSH</t>
@@ -211,7 +211,7 @@
     <t>Vit50125@123</t>
   </si>
   <si>
-    <t>(multi)50128</t>
+    <t>(MULTI)50128</t>
   </si>
   <si>
     <t>HEMAMALINI</t>
@@ -223,7 +223,7 @@
     <t>Vit50128@123</t>
   </si>
   <si>
-    <t>(multi)50131</t>
+    <t>(MULTI)50131</t>
   </si>
   <si>
     <t>JOHN SAHAYA RANI ALEX</t>
@@ -235,7 +235,7 @@
     <t>Vit50131@123</t>
   </si>
   <si>
-    <t>(multi)50135</t>
+    <t>(MULTI)50135</t>
   </si>
   <si>
     <t>PRABHAKAR V</t>
@@ -247,7 +247,7 @@
     <t>Vit50135@123</t>
   </si>
   <si>
-    <t>(multi)50137</t>
+    <t>(MULTI)50137</t>
   </si>
   <si>
     <t>GNANA SWATHIKA O V</t>
@@ -259,7 +259,7 @@
     <t>Vit50137@123</t>
   </si>
   <si>
-    <t>(multi)50138</t>
+    <t>(MULTI)50138</t>
   </si>
   <si>
     <t>VERGIN RAJA SAROBIN M</t>
@@ -271,7 +271,7 @@
     <t>Vit50138@123</t>
   </si>
   <si>
-    <t>(multi)50140</t>
+    <t>(MULTI)50140</t>
   </si>
   <si>
     <t>MUTHUNAGAI</t>
@@ -283,7 +283,7 @@
     <t>Vit50140@123</t>
   </si>
   <si>
-    <t>(multi)50142</t>
+    <t>(MULTI)50142</t>
   </si>
   <si>
     <t>SASIPRIYA P</t>
@@ -295,7 +295,7 @@
     <t>Vit50142@123</t>
   </si>
   <si>
-    <t>(multi)50146</t>
+    <t>(MULTI)50146</t>
   </si>
   <si>
     <t>RAJENDRA KUMAR K</t>
@@ -307,7 +307,7 @@
     <t>Vit50146@123</t>
   </si>
   <si>
-    <t>(multi)50147</t>
+    <t>(MULTI)50147</t>
   </si>
   <si>
     <t>KANIMOZHI G</t>
@@ -319,7 +319,7 @@
     <t>Vit50147@123</t>
   </si>
   <si>
-    <t>(multi)50148</t>
+    <t>(MULTI)50148</t>
   </si>
   <si>
     <t>TANUSHREE CHOUDHRY</t>
@@ -331,7 +331,7 @@
     <t>Vit50148@123</t>
   </si>
   <si>
-    <t>(multi)50151</t>
+    <t>(MULTI)50151</t>
   </si>
   <si>
     <t>SUGUMARAN</t>
@@ -343,7 +343,7 @@
     <t>Vit50151@123</t>
   </si>
   <si>
-    <t>(multi)50152</t>
+    <t>(MULTI)50152</t>
   </si>
   <si>
     <t>FEBIN DAYA J L</t>
@@ -355,7 +355,7 @@
     <t>Vit50152@123</t>
   </si>
   <si>
-    <t>(multi)50153</t>
+    <t>(MULTI)50153</t>
   </si>
   <si>
     <t>NITHYA VENKATESAN</t>
@@ -367,7 +367,7 @@
     <t>Vit50153@123</t>
   </si>
   <si>
-    <t>(multi)50155</t>
+    <t>(MULTI)50155</t>
   </si>
   <si>
     <t>MEENAKSHI J</t>
@@ -379,7 +379,7 @@
     <t>Vit50155@123</t>
   </si>
   <si>
-    <t>(multi)50167</t>
+    <t>(MULTI)50167</t>
   </si>
   <si>
     <t>BHASKARA RAO</t>
@@ -391,7 +391,7 @@
     <t>Vit50167@123</t>
   </si>
   <si>
-    <t>(multi)50175</t>
+    <t>(MULTI)50175</t>
   </si>
   <si>
     <t>MANIKANDAN N</t>
@@ -403,7 +403,7 @@
     <t>Vit50175@123</t>
   </si>
   <si>
-    <t>(multi)50177</t>
+    <t>(MULTI)50177</t>
   </si>
   <si>
     <t>THOMAS ABRAHAM J V</t>
@@ -415,7 +415,7 @@
     <t>Vit50177@123</t>
   </si>
   <si>
-    <t>(multi)50184</t>
+    <t>(MULTI)50184</t>
   </si>
   <si>
     <t>SAROJ KUMAR DASH</t>
@@ -427,7 +427,7 @@
     <t>Vit50184@123</t>
   </si>
   <si>
-    <t>(multi)50186</t>
+    <t>(MULTI)50186</t>
   </si>
   <si>
     <t>PARVATHI R</t>
@@ -439,7 +439,7 @@
     <t>Vit50186@123</t>
   </si>
   <si>
-    <t>(multi)50191</t>
+    <t>(MULTI)50191</t>
   </si>
   <si>
     <t>MAHALAKSHMI S</t>
@@ -451,7 +451,7 @@
     <t>Vit50191@123</t>
   </si>
   <si>
-    <t>(multi)50195</t>
+    <t>(MULTI)50195</t>
   </si>
   <si>
     <t>CAROLINE PONRAJ</t>
@@ -463,7 +463,7 @@
     <t>Vit50195@123</t>
   </si>
   <si>
-    <t>(multi)50196</t>
+    <t>(MULTI)50196</t>
   </si>
   <si>
     <t>JAGANATHAN B</t>
@@ -475,7 +475,7 @@
     <t>Vit50196@123</t>
   </si>
   <si>
-    <t>(multi)50200</t>
+    <t>(MULTI)50200</t>
   </si>
   <si>
     <t>PUNITHAVELAN N</t>
@@ -487,7 +487,7 @@
     <t>Vit50200@123</t>
   </si>
   <si>
-    <t>(multi)50201</t>
+    <t>(MULTI)50201</t>
   </si>
   <si>
     <t>UMMITY SRINIVASA RAO</t>
@@ -499,7 +499,7 @@
     <t>Vit50201@123</t>
   </si>
   <si>
-    <t>(multi)50208</t>
+    <t>(MULTI)50208</t>
   </si>
   <si>
     <t>N.GOBINATH</t>
@@ -511,7 +511,7 @@
     <t>Vit50208@123</t>
   </si>
   <si>
-    <t>(multi)50239</t>
+    <t>(MULTI)50239</t>
   </si>
   <si>
     <t>KHADAR NAWAS K</t>
@@ -523,7 +523,7 @@
     <t>Vit50239@123</t>
   </si>
   <si>
-    <t>(multi)50249</t>
+    <t>(MULTI)50249</t>
   </si>
   <si>
     <t>PRAKASH B</t>
@@ -535,7 +535,7 @@
     <t>Vit50249@123</t>
   </si>
   <si>
-    <t>(multi)50252</t>
+    <t>(MULTI)50252</t>
   </si>
   <si>
     <t>USHA KIRAN KOMMURI</t>
@@ -547,7 +547,7 @@
     <t>Vit50252@123</t>
   </si>
   <si>
-    <t>(multi)50260</t>
+    <t>(MULTI)50260</t>
   </si>
   <si>
     <t>NIRAJ KUMAR</t>
@@ -559,7 +559,7 @@
     <t>Vit50260@123</t>
   </si>
   <si>
-    <t>(multi)50264</t>
+    <t>(MULTI)50264</t>
   </si>
   <si>
     <t>SENTHIL KUMAR N</t>
@@ -571,7 +571,7 @@
     <t>Vit50264@123</t>
   </si>
   <si>
-    <t>(multi)50265</t>
+    <t>(MULTI)50265</t>
   </si>
   <si>
     <t>LAVANYA V</t>
@@ -583,7 +583,7 @@
     <t>Vit50265@123</t>
   </si>
   <si>
-    <t>(multi)50270</t>
+    <t>(MULTI)50270</t>
   </si>
   <si>
     <t>VIJAYALAKSHMI A</t>
@@ -595,7 +595,7 @@
     <t>Vit50270@123</t>
   </si>
   <si>
-    <t>(multi)50273</t>
+    <t>(MULTI)50273</t>
   </si>
   <si>
     <t>MEERA P S</t>
@@ -607,7 +607,7 @@
     <t>Vit50273@123</t>
   </si>
   <si>
-    <t>(multi)50275</t>
+    <t>(MULTI)50275</t>
   </si>
   <si>
     <t>SRI RAMALAKSHMI P</t>
@@ -619,7 +619,7 @@
     <t>Vit50275@123</t>
   </si>
   <si>
-    <t>(multi)50276</t>
+    <t>(MULTI)50276</t>
   </si>
   <si>
     <t>B V A N S S PRABHAKAR RAO</t>
@@ -631,7 +631,7 @@
     <t>Vit50276@123</t>
   </si>
   <si>
-    <t>(multi)50278</t>
+    <t>(MULTI)50278</t>
   </si>
   <si>
     <t>SAKTHIVEL S M</t>
@@ -643,7 +643,7 @@
     <t>Vit50278@123</t>
   </si>
   <si>
-    <t>(multi)50282</t>
+    <t>(MULTI)50282</t>
   </si>
   <si>
     <t>ANANTHA KRISHNAN V</t>
@@ -655,7 +655,7 @@
     <t>Vit50282@123</t>
   </si>
   <si>
-    <t>(multi)50283</t>
+    <t>(MULTI)50283</t>
   </si>
   <si>
     <t>MANIKANDAN P</t>
@@ -667,7 +667,7 @@
     <t>Vit50283@123</t>
   </si>
   <si>
-    <t>(multi)50287</t>
+    <t>(MULTI)50287</t>
   </si>
   <si>
     <t>M. PRABHAKAR</t>
@@ -679,7 +679,7 @@
     <t>Vit50287@123</t>
   </si>
   <si>
-    <t>(multi)50289</t>
+    <t>(MULTI)50289</t>
   </si>
   <si>
     <t>M. PREMALATHA</t>
@@ -691,7 +691,7 @@
     <t>Vit50289@123</t>
   </si>
   <si>
-    <t>(multi)50290</t>
+    <t>(MULTI)50290</t>
   </si>
   <si>
     <t>B. NAGAJAYANTHI</t>
@@ -703,7 +703,7 @@
     <t>Vit50290@123</t>
   </si>
   <si>
-    <t>(multi)50292</t>
+    <t>(MULTI)50292</t>
   </si>
   <si>
     <t>RADHA S</t>
@@ -715,7 +715,7 @@
     <t>Vit50292@123</t>
   </si>
   <si>
-    <t>(multi)50293</t>
+    <t>(MULTI)50293</t>
   </si>
   <si>
     <t>ANITH NELLERI</t>
@@ -727,7 +727,7 @@
     <t>Vit50293@123</t>
   </si>
   <si>
-    <t>(multi)50299</t>
+    <t>(MULTI)50299</t>
   </si>
   <si>
     <t>S. BHARATHI RAJA</t>
@@ -739,7 +739,7 @@
     <t>Vit50299@123</t>
   </si>
   <si>
-    <t>(multi)50302</t>
+    <t>(MULTI)50302</t>
   </si>
   <si>
     <t>TAMIL SELVAN P</t>
@@ -751,7 +751,7 @@
     <t>Vit50302@123</t>
   </si>
   <si>
-    <t>(multi)50305</t>
+    <t>(MULTI)50305</t>
   </si>
   <si>
     <t>HELEN SANTHI M</t>
@@ -763,7 +763,7 @@
     <t>Vit50305@123</t>
   </si>
   <si>
-    <t>(multi)50307</t>
+    <t>(MULTI)50307</t>
   </si>
   <si>
     <t>PRIYAADHARSHINI M</t>
@@ -775,7 +775,7 @@
     <t>Vit50307@123</t>
   </si>
   <si>
-    <t>(multi)50309</t>
+    <t>(MULTI)50309</t>
   </si>
   <si>
     <t>MOHAN K</t>
@@ -787,7 +787,7 @@
     <t>Vit50309@123</t>
   </si>
   <si>
-    <t>(multi)50310</t>
+    <t>(MULTI)50310</t>
   </si>
   <si>
     <t>PRATHIBA A</t>
@@ -799,7 +799,7 @@
     <t>Vit50310@123</t>
   </si>
   <si>
-    <t>(multi)50315</t>
+    <t>(MULTI)50315</t>
   </si>
   <si>
     <t>JAYARAM B</t>
@@ -811,7 +811,7 @@
     <t>Vit50315@123</t>
   </si>
   <si>
-    <t>(multi)50316</t>
+    <t>(MULTI)50316</t>
   </si>
   <si>
     <t>JOSEPH DANIEL</t>
@@ -823,7 +823,7 @@
     <t>Vit50316@123</t>
   </si>
   <si>
-    <t>(multi)50318</t>
+    <t>(MULTI)50318</t>
   </si>
   <si>
     <t>NIVEDITA M</t>
@@ -835,7 +835,7 @@
     <t>Vit50318@123</t>
   </si>
   <si>
-    <t>(multi)50319</t>
+    <t>(MULTI)50319</t>
   </si>
   <si>
     <t>BHARADWAJA KUMAR</t>
@@ -847,7 +847,7 @@
     <t>Vit50319@123</t>
   </si>
   <si>
-    <t>(multi)50322</t>
+    <t>(MULTI)50322</t>
   </si>
   <si>
     <t>JAYASUDHA M</t>
@@ -859,7 +859,7 @@
     <t>Vit50322@123</t>
   </si>
   <si>
-    <t>(multi)50329</t>
+    <t>(MULTI)50329</t>
   </si>
   <si>
     <t>PANKAJ SHUKLA</t>
@@ -871,7 +871,7 @@
     <t>Vit50329@123</t>
   </si>
   <si>
-    <t>(multi)50330</t>
+    <t>(MULTI)50330</t>
   </si>
   <si>
     <t>ELANGO M</t>
@@ -883,7 +883,7 @@
     <t>Vit50330@123</t>
   </si>
   <si>
-    <t>(multi)50331</t>
+    <t>(MULTI)50331</t>
   </si>
   <si>
     <t>SENTHIL KUMAR M</t>
@@ -895,7 +895,7 @@
     <t>Vit50331@123</t>
   </si>
   <si>
-    <t>(multi)50335</t>
+    <t>(MULTI)50335</t>
   </si>
   <si>
     <t>DAVIDSON JEBASEELAN</t>
@@ -907,7 +907,7 @@
     <t>Vit50335@123</t>
   </si>
   <si>
-    <t>(multi)50337</t>
+    <t>(MULTI)50337</t>
   </si>
   <si>
     <t>ANNAMALAI K</t>
@@ -919,7 +919,7 @@
     <t>Vit50337@123</t>
   </si>
   <si>
-    <t>(multi)50345</t>
+    <t>(MULTI)50345</t>
   </si>
   <si>
     <t>ANGELINE EZHILARASI G</t>
@@ -931,7 +931,7 @@
     <t>Vit50345@123</t>
   </si>
   <si>
-    <t>(multi)50346</t>
+    <t>(MULTI)50346</t>
   </si>
   <si>
     <t>BERIN GREENI A</t>
@@ -943,7 +943,7 @@
     <t>Vit50346@123</t>
   </si>
   <si>
-    <t>(multi)50348</t>
+    <t>(MULTI)50348</t>
   </si>
   <si>
     <t>DHANASEKAR S</t>
@@ -955,7 +955,7 @@
     <t>Vit50348@123</t>
   </si>
   <si>
-    <t>(multi)50349</t>
+    <t>(MULTI)50349</t>
   </si>
   <si>
     <t>SENTHILPANDIAN M</t>
@@ -967,7 +967,7 @@
     <t>Vit50349@123</t>
   </si>
   <si>
-    <t>(multi)50352</t>
+    <t>(MULTI)50352</t>
   </si>
   <si>
     <t>JENILA LIVINGSTON L M</t>
@@ -979,7 +979,7 @@
     <t>Vit50352@123</t>
   </si>
   <si>
-    <t>(multi)50358</t>
+    <t>(MULTI)50358</t>
   </si>
   <si>
     <t>MANOJ KUMAR R</t>
@@ -991,7 +991,7 @@
     <t>Vit50358@123</t>
   </si>
   <si>
-    <t>(multi)50359</t>
+    <t>(MULTI)50359</t>
   </si>
   <si>
     <t>REKHA D</t>
@@ -1003,7 +1003,7 @@
     <t>Vit50359@123</t>
   </si>
   <si>
-    <t>(multi)50361</t>
+    <t>(MULTI)50361</t>
   </si>
   <si>
     <t>YAMINI SREEVALLI I</t>
@@ -1015,7 +1015,7 @@
     <t>Vit50361@123</t>
   </si>
   <si>
-    <t>(multi)50369</t>
+    <t>(MULTI)50369</t>
   </si>
   <si>
     <t>LAKSHMI B</t>
@@ -1027,7 +1027,7 @@
     <t>Vit50369@123</t>
   </si>
   <si>
-    <t>(multi)50370</t>
+    <t>(MULTI)50370</t>
   </si>
   <si>
     <t>RAJESH KUMAR</t>
@@ -1039,7 +1039,7 @@
     <t>Vit50370@123</t>
   </si>
   <si>
-    <t>(multi)50375</t>
+    <t>(MULTI)50375</t>
   </si>
   <si>
     <t>LENIN N C</t>
@@ -1051,7 +1051,7 @@
     <t>Vit50375@123</t>
   </si>
   <si>
-    <t>(multi)50381</t>
+    <t>(MULTI)50381</t>
   </si>
   <si>
     <t>CHENDUR KUMARAN R</t>
@@ -1063,7 +1063,7 @@
     <t>Vit50381@123</t>
   </si>
   <si>
-    <t>(multi)50384</t>
+    <t>(MULTI)50384</t>
   </si>
   <si>
     <t>NEELANARAYANAN V</t>
@@ -1075,7 +1075,7 @@
     <t>Vit50384@123</t>
   </si>
   <si>
-    <t>(multi)50385</t>
+    <t>(MULTI)50385</t>
   </si>
   <si>
     <t>VIGNESWARAN T</t>
@@ -1087,7 +1087,7 @@
     <t>Vit50385@123</t>
   </si>
   <si>
-    <t>(multi)50386</t>
+    <t>(MULTI)50386</t>
   </si>
   <si>
     <t>ABDUL QUADIR MD</t>
@@ -1099,7 +1099,7 @@
     <t>Vit50386@123</t>
   </si>
   <si>
-    <t>(multi)50390</t>
+    <t>(MULTI)50390</t>
   </si>
   <si>
     <t>ALOK CHAUHAN</t>
@@ -1111,7 +1111,7 @@
     <t>Vit50390@123</t>
   </si>
   <si>
-    <t>(multi)50391</t>
+    <t>(MULTI)50391</t>
   </si>
   <si>
     <t>RABINDRA KUMAR SINGH</t>
@@ -1123,7 +1123,7 @@
     <t>Vit50391@123</t>
   </si>
   <si>
-    <t>(multi)50392</t>
+    <t>(MULTI)50392</t>
   </si>
   <si>
     <t>SYED IBRAHIM S P</t>
@@ -1135,7 +1135,7 @@
     <t>Vit50392@123</t>
   </si>
   <si>
-    <t>(multi)50395</t>
+    <t>(MULTI)50395</t>
   </si>
   <si>
     <t>SREEKANTH DONDAPATI</t>
@@ -1147,7 +1147,7 @@
     <t>Vit50395@123</t>
   </si>
   <si>
-    <t>(multi)50398</t>
+    <t>(MULTI)50398</t>
   </si>
   <si>
     <t>SIVABALAKRISHNAN M</t>
@@ -1159,7 +1159,7 @@
     <t>Vit50398@123</t>
   </si>
   <si>
-    <t>(multi)50401</t>
+    <t>(MULTI)50401</t>
   </si>
   <si>
     <t>PUNITHA K</t>
@@ -1171,7 +1171,7 @@
     <t>Vit50401@123</t>
   </si>
   <si>
-    <t>(multi)50403</t>
+    <t>(MULTI)50403</t>
   </si>
   <si>
     <t>RAJESH M</t>
@@ -1183,7 +1183,7 @@
     <t>Vit50403@123</t>
   </si>
   <si>
-    <t>(multi)50404</t>
+    <t>(MULTI)50404</t>
   </si>
   <si>
     <t>RAJIV VINCENT</t>
@@ -1195,7 +1195,7 @@
     <t>Vit50404@123</t>
   </si>
   <si>
-    <t>(multi)50407</t>
+    <t>(MULTI)50407</t>
   </si>
   <si>
     <t>MUTHULAKSHMI S</t>
@@ -1207,7 +1207,7 @@
     <t>Vit50407@123</t>
   </si>
   <si>
-    <t>(multi)50408</t>
+    <t>(MULTI)50408</t>
   </si>
   <si>
     <t>ANUSOOYA G</t>
@@ -1219,7 +1219,7 @@
     <t>Vit50408@123</t>
   </si>
   <si>
-    <t>(multi)50409</t>
+    <t>(MULTI)50409</t>
   </si>
   <si>
     <t>RALPH SAMUEL THANGARAJ</t>
@@ -1231,7 +1231,7 @@
     <t>Vit50409@123</t>
   </si>
   <si>
-    <t>(multi)50410</t>
+    <t>(MULTI)50410</t>
   </si>
   <si>
     <t>SANDHYA P</t>
@@ -1243,7 +1243,7 @@
     <t>Vit50410@123</t>
   </si>
   <si>
-    <t>(multi)50411</t>
+    <t>(MULTI)50411</t>
   </si>
   <si>
     <t>GUGA PRIYA G</t>
@@ -1255,7 +1255,7 @@
     <t>Vit50411@123</t>
   </si>
   <si>
-    <t>(multi)50414</t>
+    <t>(MULTI)50414</t>
   </si>
   <si>
     <t>JAYA VIGNESH T</t>
@@ -1267,7 +1267,7 @@
     <t>Vit50414@123</t>
   </si>
   <si>
-    <t>(multi)50416</t>
+    <t>(MULTI)50416</t>
   </si>
   <si>
     <t>SARANYA NAIR M</t>
@@ -1279,7 +1279,7 @@
     <t>Vit50416@123</t>
   </si>
   <si>
-    <t>(multi)50418</t>
+    <t>(MULTI)50418</t>
   </si>
   <si>
     <t>CHANDRASEKARAN N</t>
@@ -1291,7 +1291,7 @@
     <t>Vit50418@123</t>
   </si>
   <si>
-    <t>(multi)50419</t>
+    <t>(MULTI)50419</t>
   </si>
   <si>
     <t>PEER FATHIMA A</t>
@@ -1303,7 +1303,7 @@
     <t>Vit50419@123</t>
   </si>
   <si>
-    <t>(multi)50421</t>
+    <t>(MULTI)50421</t>
   </si>
   <si>
     <t>RADHA</t>
@@ -1315,7 +1315,7 @@
     <t>Vit50421@123</t>
   </si>
   <si>
-    <t>(multi)50423</t>
+    <t>(MULTI)50423</t>
   </si>
   <si>
     <t>PRAKASH V</t>
@@ -1327,7 +1327,7 @@
     <t>Vit50423@123</t>
   </si>
   <si>
-    <t>(multi)50425</t>
+    <t>(MULTI)50425</t>
   </si>
   <si>
     <t>RAMESH R</t>
@@ -1339,7 +1339,7 @@
     <t>Vit50425@123</t>
   </si>
   <si>
-    <t>(multi)50426</t>
+    <t>(MULTI)50426</t>
   </si>
   <si>
     <t>ABRAHAM SUDHARSON PONRAJ</t>
@@ -1351,7 +1351,7 @@
     <t>Vit50426@123</t>
   </si>
   <si>
-    <t>(multi)50427</t>
+    <t>(MULTI)50427</t>
   </si>
   <si>
     <t>SRIVATSAN K</t>
@@ -1363,7 +1363,7 @@
     <t>Vit50427@123</t>
   </si>
   <si>
-    <t>(multi)50428</t>
+    <t>(MULTI)50428</t>
   </si>
   <si>
     <t>UMADEVI S</t>
@@ -1375,7 +1375,7 @@
     <t>Vit50428@123</t>
   </si>
   <si>
-    <t>(multi)50430</t>
+    <t>(MULTI)50430</t>
   </si>
   <si>
     <t>PRABHAKARAN R</t>
@@ -1387,7 +1387,7 @@
     <t>Vit50430@123</t>
   </si>
   <si>
-    <t>(multi)50431</t>
+    <t>(MULTI)50431</t>
   </si>
   <si>
     <t>SRUTHA KEERTHI B</t>
@@ -1399,7 +1399,7 @@
     <t>Vit50431@123</t>
   </si>
   <si>
-    <t>(multi)50432</t>
+    <t>(MULTI)50432</t>
   </si>
   <si>
     <t>SHOLA USHA RANI</t>
@@ -1411,7 +1411,7 @@
     <t>Vit50432@123</t>
   </si>
   <si>
-    <t>(multi)50433</t>
+    <t>(MULTI)50433</t>
   </si>
   <si>
     <t>BALAMURUGAN P</t>
@@ -1423,7 +1423,7 @@
     <t>Vit50433@123</t>
   </si>
   <si>
-    <t>(multi)50437</t>
+    <t>(MULTI)50437</t>
   </si>
   <si>
     <t>LENIN BABU M C</t>
@@ -1435,7 +1435,7 @@
     <t>Vit50437@123</t>
   </si>
   <si>
-    <t>(multi)50438</t>
+    <t>(MULTI)50438</t>
   </si>
   <si>
     <t>SUGANYA G</t>
@@ -1447,7 +1447,7 @@
     <t>Vit50438@123</t>
   </si>
   <si>
-    <t>(multi)50439</t>
+    <t>(MULTI)50439</t>
   </si>
   <si>
     <t>NILANJAN TEWARI</t>
@@ -1459,7 +1459,7 @@
     <t>Vit50439@123</t>
   </si>
   <si>
-    <t>(multi)50440</t>
+    <t>(MULTI)50440</t>
   </si>
   <si>
     <t>SRIDHAR R</t>
@@ -1471,7 +1471,7 @@
     <t>Vit50440@123</t>
   </si>
   <si>
-    <t>(multi)50443</t>
+    <t>(MULTI)50443</t>
   </si>
   <si>
     <t>NITHYANANDAM P</t>
@@ -1483,7 +1483,7 @@
     <t>Vit50443@123</t>
   </si>
   <si>
-    <t>(multi)50444</t>
+    <t>(MULTI)50444</t>
   </si>
   <si>
     <t>AROCKIA SELVAKUMAR</t>
@@ -1495,7 +1495,7 @@
     <t>Vit50444@123</t>
   </si>
   <si>
-    <t>(multi)50455</t>
+    <t>(MULTI)50455</t>
   </si>
   <si>
     <t>JAMUNA K</t>
@@ -1507,7 +1507,7 @@
     <t>Vit50455@123</t>
   </si>
   <si>
-    <t>(multi)50458</t>
+    <t>(MULTI)50458</t>
   </si>
   <si>
     <t>ELAVENIL S</t>
@@ -1519,7 +1519,7 @@
     <t>Vit50458@123</t>
   </si>
   <si>
-    <t>(multi)50466</t>
+    <t>(MULTI)50466</t>
   </si>
   <si>
     <t>MANIMARAN R</t>
@@ -1531,7 +1531,7 @@
     <t>Vit50466@123</t>
   </si>
   <si>
-    <t>(multi)50501</t>
+    <t>(MULTI)50501</t>
   </si>
   <si>
     <t>DEIVANATHAN R</t>
@@ -1543,7 +1543,7 @@
     <t>Vit50501@123</t>
   </si>
   <si>
-    <t>(multi)50504</t>
+    <t>(MULTI)50504</t>
   </si>
   <si>
     <t>KARTHIKEYAN K</t>
@@ -1555,7 +1555,7 @@
     <t>Vit50504@123</t>
   </si>
   <si>
-    <t>(multi)50505</t>
+    <t>(MULTI)50505</t>
   </si>
   <si>
     <t>VASUGI K</t>
@@ -1567,7 +1567,7 @@
     <t>Vit50505@123</t>
   </si>
   <si>
-    <t>(multi)50506</t>
+    <t>(MULTI)50506</t>
   </si>
   <si>
     <t>VENUGOPAL T</t>
@@ -1579,7 +1579,7 @@
     <t>Vit50506@123</t>
   </si>
   <si>
-    <t>(multi)50507</t>
+    <t>(MULTI)50507</t>
   </si>
   <si>
     <t>GOPINATH MUDHANA</t>
@@ -1591,7 +1591,7 @@
     <t>Vit50507@123</t>
   </si>
   <si>
-    <t>(multi)50564</t>
+    <t>(MULTI)50564</t>
   </si>
   <si>
     <t>HEMANTH C</t>
@@ -1603,7 +1603,7 @@
     <t>Vit50564@123</t>
   </si>
   <si>
-    <t>(multi)50565</t>
+    <t>(MULTI)50565</t>
   </si>
   <si>
     <t>SUBBULEKSHMI D</t>
@@ -1615,7 +1615,7 @@
     <t>Vit50565@123</t>
   </si>
   <si>
-    <t>(multi)50570</t>
+    <t>(MULTI)50570</t>
   </si>
   <si>
     <t>ANGALAESWARI S</t>
@@ -1627,7 +1627,7 @@
     <t>Vit50570@123</t>
   </si>
   <si>
-    <t>(multi)50571</t>
+    <t>(MULTI)50571</t>
   </si>
   <si>
     <t>DEEPA T</t>
@@ -1639,7 +1639,7 @@
     <t>Vit50571@123</t>
   </si>
   <si>
-    <t>(multi)50572</t>
+    <t>(MULTI)50572</t>
   </si>
   <si>
     <t>IYSWARYA ANNAPOORANI K</t>
@@ -1651,7 +1651,7 @@
     <t>Vit50572@123</t>
   </si>
   <si>
-    <t>(multi)50577</t>
+    <t>(MULTI)50577</t>
   </si>
   <si>
     <t>RENTA CHINTALA BHARGAVI</t>
@@ -1663,7 +1663,7 @@
     <t>Vit50577@123</t>
   </si>
   <si>
-    <t>(multi)50578</t>
+    <t>(MULTI)50578</t>
   </si>
   <si>
     <t>CHRISTO MICHAEL T</t>
@@ -1675,7 +1675,7 @@
     <t>Vit50578@123</t>
   </si>
   <si>
-    <t>(multi)50579</t>
+    <t>(MULTI)50579</t>
   </si>
   <si>
     <t>KRISHNENDU BISWAS</t>
@@ -1687,7 +1687,7 @@
     <t>Vit50579@123</t>
   </si>
   <si>
-    <t>(multi)50582</t>
+    <t>(MULTI)50582</t>
   </si>
   <si>
     <t>KURUSEELAN S</t>
@@ -1699,7 +1699,7 @@
     <t>Vit50582@123</t>
   </si>
   <si>
-    <t>(multi)50583</t>
+    <t>(MULTI)50583</t>
   </si>
   <si>
     <t>RAVI V</t>
@@ -1711,7 +1711,7 @@
     <t>Vit50583@123</t>
   </si>
   <si>
-    <t>(multi)50586</t>
+    <t>(MULTI)50586</t>
   </si>
   <si>
     <t>SANJIT DAS</t>
@@ -1723,7 +1723,7 @@
     <t>Vit50586@123</t>
   </si>
   <si>
-    <t>(multi)50587</t>
+    <t>(MULTI)50587</t>
   </si>
   <si>
     <t>GEETHA S</t>
@@ -1735,7 +1735,7 @@
     <t>Vit50587@123</t>
   </si>
   <si>
-    <t>(multi)50588</t>
+    <t>(MULTI)50588</t>
   </si>
   <si>
     <t>NAVAMATHAVAN R</t>
@@ -1747,7 +1747,7 @@
     <t>Vit50588@123</t>
   </si>
   <si>
-    <t>(multi)50591</t>
+    <t>(MULTI)50591</t>
   </si>
   <si>
     <t>BALA MURUGAN M S</t>
@@ -1759,7 +1759,7 @@
     <t>Vit50591@123</t>
   </si>
   <si>
-    <t>(multi)50592</t>
+    <t>(MULTI)50592</t>
   </si>
   <si>
     <t>SARAVANAKUMAR R</t>
@@ -1771,7 +1771,7 @@
     <t>Vit50592@123</t>
   </si>
   <si>
-    <t>(multi)50593</t>
+    <t>(MULTI)50593</t>
   </si>
   <si>
     <t>RAGHUKIRAN NADIMPALLI</t>
@@ -1783,7 +1783,7 @@
     <t>Vit50593@123</t>
   </si>
   <si>
-    <t>(multi)50594</t>
+    <t>(MULTI)50594</t>
   </si>
   <si>
     <t>VAITHILINGAM C</t>
@@ -1795,7 +1795,7 @@
     <t>Vit50594@123</t>
   </si>
   <si>
-    <t>(multi)50596</t>
+    <t>(MULTI)50596</t>
   </si>
   <si>
     <t>BINU BEN JOSE D R</t>
@@ -1807,7 +1807,7 @@
     <t>Vit50596@123</t>
   </si>
   <si>
-    <t>(multi)50597</t>
+    <t>(MULTI)50597</t>
   </si>
   <si>
     <t>VINAYAGAMURTHY G</t>
@@ -1819,7 +1819,7 @@
     <t>Vit50597@123</t>
   </si>
   <si>
-    <t>(multi)50598</t>
+    <t>(MULTI)50598</t>
   </si>
   <si>
     <t>DAVID MAXIM GURURAJ A</t>
@@ -1831,7 +1831,7 @@
     <t>Vit50598@123</t>
   </si>
   <si>
-    <t>(multi)50604</t>
+    <t>(MULTI)50604</t>
   </si>
   <si>
     <t>SANGEETHA R G</t>
@@ -1843,7 +1843,7 @@
     <t>Vit50604@123</t>
   </si>
   <si>
-    <t>(multi)50610</t>
+    <t>(MULTI)50610</t>
   </si>
   <si>
     <t>ARUN KUMAR A</t>
@@ -1855,7 +1855,7 @@
     <t>Vit50610@123</t>
   </si>
   <si>
-    <t>(multi)50611</t>
+    <t>(MULTI)50611</t>
   </si>
   <si>
     <t>ABHISHEK KUMAR SINGH</t>
@@ -1867,7 +1867,7 @@
     <t>Vit50611@123</t>
   </si>
   <si>
-    <t>(multi)50616</t>
+    <t>(MULTI)50616</t>
   </si>
   <si>
     <t>JANAKI MEENA M</t>
@@ -1879,7 +1879,7 @@
     <t>Vit50616@123</t>
   </si>
   <si>
-    <t>(multi)50619</t>
+    <t>(MULTI)50619</t>
   </si>
   <si>
     <t>BERLIN HENCY V</t>
@@ -1891,7 +1891,7 @@
     <t>Vit50619@123</t>
   </si>
   <si>
-    <t>(multi)50621</t>
+    <t>(MULTI)50621</t>
   </si>
   <si>
     <t>ANNIS FATHIMA A</t>
@@ -1903,7 +1903,7 @@
     <t>Vit50621@123</t>
   </si>
   <si>
-    <t>(multi)50622</t>
+    <t>(MULTI)50622</t>
   </si>
   <si>
     <t>JAFFERSON J M</t>
@@ -1915,7 +1915,7 @@
     <t>Vit50622@123</t>
   </si>
   <si>
-    <t>(multi)50636</t>
+    <t>(MULTI)50636</t>
   </si>
   <si>
     <t>REVATHI G K</t>
@@ -1927,7 +1927,7 @@
     <t>Vit50636@123</t>
   </si>
   <si>
-    <t>(multi)50729</t>
+    <t>(MULTI)50729</t>
   </si>
   <si>
     <t>BINDU B</t>
@@ -1939,7 +1939,7 @@
     <t>Vit50729@123</t>
   </si>
   <si>
-    <t>(multi)50730</t>
+    <t>(MULTI)50730</t>
   </si>
   <si>
     <t>GIRIDHARAN A</t>
@@ -1951,7 +1951,7 @@
     <t>Vit50730@123</t>
   </si>
   <si>
-    <t>(multi)50731</t>
+    <t>(MULTI)50731</t>
   </si>
   <si>
     <t>JEYANTHI S</t>
@@ -1963,7 +1963,7 @@
     <t>Vit50731@123</t>
   </si>
   <si>
-    <t>(multi)50740</t>
+    <t>(MULTI)50740</t>
   </si>
   <si>
     <t>UMAYAL C</t>
@@ -1975,7 +1975,7 @@
     <t>Vit50740@123</t>
   </si>
   <si>
-    <t>(multi)50766</t>
+    <t>(MULTI)50766</t>
   </si>
   <si>
     <t>JAYANTA PARUI</t>
@@ -1987,7 +1987,7 @@
     <t>Vit50766@123</t>
   </si>
   <si>
-    <t>(multi)50767</t>
+    <t>(MULTI)50767</t>
   </si>
   <si>
     <t>SWEETLIN HEMALATHA C</t>
@@ -1999,7 +1999,7 @@
     <t>Vit50767@123</t>
   </si>
   <si>
-    <t>(multi)50769</t>
+    <t>(MULTI)50769</t>
   </si>
   <si>
     <t>DEVAPRAKASAM D</t>
@@ -2011,7 +2011,7 @@
     <t>Vit50769@123</t>
   </si>
   <si>
-    <t>(multi)50772</t>
+    <t>(MULTI)50772</t>
   </si>
   <si>
     <t>NATHIYA N</t>
@@ -2023,7 +2023,7 @@
     <t>Vit50772@123</t>
   </si>
   <si>
-    <t>(multi)50776</t>
+    <t>(MULTI)50776</t>
   </si>
   <si>
     <t>PREMALATHA L</t>
@@ -2035,7 +2035,7 @@
     <t>Vit50776@123</t>
   </si>
   <si>
-    <t>(multi)50777</t>
+    <t>(MULTI)50777</t>
   </si>
   <si>
     <t>VELMATHI G</t>
@@ -2047,7 +2047,7 @@
     <t>Vit50777@123</t>
   </si>
   <si>
-    <t>(multi)50780</t>
+    <t>(MULTI)50780</t>
   </si>
   <si>
     <t>SIVASUBRAMANIAN A</t>
@@ -2059,7 +2059,7 @@
     <t>Vit50780@123</t>
   </si>
   <si>
-    <t>(multi)50786</t>
+    <t>(MULTI)50786</t>
   </si>
   <si>
     <t>MOHAMED IMRAN A</t>
@@ -2071,7 +2071,7 @@
     <t>Vit50786@123</t>
   </si>
   <si>
-    <t>(multi)50851</t>
+    <t>(MULTI)50851</t>
   </si>
   <si>
     <t>GARGI RAINA</t>
@@ -2083,7 +2083,7 @@
     <t>Vit50851@123</t>
   </si>
   <si>
-    <t>(multi)50863</t>
+    <t>(MULTI)50863</t>
   </si>
   <si>
     <t>KARTHIK R</t>
@@ -2095,7 +2095,7 @@
     <t>Vit50863@123</t>
   </si>
   <si>
-    <t>(multi)50879</t>
+    <t>(MULTI)50879</t>
   </si>
   <si>
     <t>RAJALAKSHMI R</t>
@@ -2107,7 +2107,7 @@
     <t>Vit50879@123</t>
   </si>
   <si>
-    <t>(multi)50906</t>
+    <t>(MULTI)50906</t>
   </si>
   <si>
     <t>SOFANA REKA S</t>
@@ -2119,7 +2119,7 @@
     <t>Vit50906@123</t>
   </si>
   <si>
-    <t>(multi)50908</t>
+    <t>(MULTI)50908</t>
   </si>
   <si>
     <t>VYDEKI D</t>
@@ -2131,7 +2131,7 @@
     <t>Vit50908@123</t>
   </si>
   <si>
-    <t>(multi)50911</t>
+    <t>(MULTI)50911</t>
   </si>
   <si>
     <t>SUGANTHI K</t>
@@ -2143,7 +2143,7 @@
     <t>Vit50911@123</t>
   </si>
   <si>
-    <t>(multi)50912</t>
+    <t>(MULTI)50912</t>
   </si>
   <si>
     <t>ARUL R</t>
@@ -2155,7 +2155,7 @@
     <t>Vit50912@123</t>
   </si>
   <si>
-    <t>(multi)50915</t>
+    <t>(MULTI)50915</t>
   </si>
   <si>
     <t>JAYAPRAGASH R</t>
@@ -2167,7 +2167,7 @@
     <t>Vit50915@123</t>
   </si>
   <si>
-    <t>(multi)50917</t>
+    <t>(MULTI)50917</t>
   </si>
   <si>
     <t>SANTOSH G</t>
@@ -2179,7 +2179,7 @@
     <t>Vit50917@123</t>
   </si>
   <si>
-    <t>(multi)50920</t>
+    <t>(MULTI)50920</t>
   </si>
   <si>
     <t>LAKSHMI PATHI JAKKAMPUTI</t>
@@ -2191,7 +2191,7 @@
     <t>Vit50920@123</t>
   </si>
   <si>
-    <t>(multi)50923</t>
+    <t>(MULTI)50923</t>
   </si>
   <si>
     <t>SUMATHI V</t>
@@ -2203,7 +2203,7 @@
     <t>Vit50923@123</t>
   </si>
   <si>
-    <t>(multi)50924</t>
+    <t>(MULTI)50924</t>
   </si>
   <si>
     <t>BALAMURALI M M</t>
@@ -2215,7 +2215,7 @@
     <t>Vit50924@123</t>
   </si>
   <si>
-    <t>(multi)50926</t>
+    <t>(MULTI)50926</t>
   </si>
   <si>
     <t>JAYANTHI R</t>
@@ -2227,7 +2227,7 @@
     <t>Vit50926@123</t>
   </si>
   <si>
-    <t>(multi)51011</t>
+    <t>(MULTI)51011</t>
   </si>
   <si>
     <t>HARISH R</t>
@@ -2239,7 +2239,7 @@
     <t>Vit51011@123</t>
   </si>
   <si>
-    <t>(multi)51012</t>
+    <t>(MULTI)51012</t>
   </si>
   <si>
     <t>MOHAN R</t>
@@ -2251,7 +2251,7 @@
     <t>Vit51012@123</t>
   </si>
   <si>
-    <t>(multi)51016</t>
+    <t>(MULTI)51016</t>
   </si>
   <si>
     <t>DEVI YAMINI S</t>
@@ -2263,7 +2263,7 @@
     <t>Vit51016@123</t>
   </si>
   <si>
-    <t>(multi)51019</t>
+    <t>(MULTI)51019</t>
   </si>
   <si>
     <t>POULOMI DE</t>
@@ -2275,7 +2275,7 @@
     <t>Vit51019@123</t>
   </si>
   <si>
-    <t>(multi)51020</t>
+    <t>(MULTI)51020</t>
   </si>
   <si>
     <t>VIDHYA V</t>
@@ -2287,7 +2287,7 @@
     <t>Vit51020@123</t>
   </si>
   <si>
-    <t>(multi)51141</t>
+    <t>(MULTI)51141</t>
   </si>
   <si>
     <t>JAYAGOPAL R</t>
@@ -2299,7 +2299,7 @@
     <t>Vit51141@123</t>
   </si>
   <si>
-    <t>(multi)51142</t>
+    <t>(MULTI)51142</t>
   </si>
   <si>
     <t>JANI ANBARASI L</t>
@@ -2311,7 +2311,7 @@
     <t>Vit51142@123</t>
   </si>
   <si>
-    <t>(multi)51151</t>
+    <t>(MULTI)51151</t>
   </si>
   <si>
     <t>MILIND SHRINIVAS DANGATE</t>
@@ -2323,7 +2323,7 @@
     <t>Vit51151@123</t>
   </si>
   <si>
-    <t>(multi)51325</t>
+    <t>(MULTI)51325</t>
   </si>
   <si>
     <t>PRASAD M</t>
@@ -2335,7 +2335,7 @@
     <t>Vit51325@123</t>
   </si>
   <si>
-    <t>(multi)51327</t>
+    <t>(MULTI)51327</t>
   </si>
   <si>
     <t>M. BRAVEEN</t>
@@ -2347,7 +2347,7 @@
     <t>Vit51327@123</t>
   </si>
   <si>
-    <t>(multi)51328</t>
+    <t>(MULTI)51328</t>
   </si>
   <si>
     <t>V. MUTHUMANIKANDAN</t>
@@ -2359,7 +2359,7 @@
     <t>Vit51328@123</t>
   </si>
   <si>
-    <t>(multi)51330</t>
+    <t>(MULTI)51330</t>
   </si>
   <si>
     <t>MAANVIZHI M</t>
@@ -2371,7 +2371,7 @@
     <t>Vit51330@123</t>
   </si>
   <si>
-    <t>(multi)51334</t>
+    <t>(MULTI)51334</t>
   </si>
   <si>
     <t>SELVAKUMAR</t>
@@ -2383,7 +2383,7 @@
     <t>Vit51334@123</t>
   </si>
   <si>
-    <t>(multi)51339</t>
+    <t>(MULTI)51339</t>
   </si>
   <si>
     <t>SK AYESHA</t>
@@ -2395,7 +2395,7 @@
     <t>Vit51339@123</t>
   </si>
   <si>
-    <t>(multi)51344</t>
+    <t>(MULTI)51344</t>
   </si>
   <si>
     <t>RADHIKA SELVAMANI</t>
@@ -2407,7 +2407,7 @@
     <t>Vit51344@123</t>
   </si>
   <si>
-    <t>(multi)51347</t>
+    <t>(MULTI)51347</t>
   </si>
   <si>
     <t>BHUVANESWARI</t>
@@ -2419,7 +2419,7 @@
     <t>Vit51347@123</t>
   </si>
   <si>
-    <t>(multi)51348</t>
+    <t>(MULTI)51348</t>
   </si>
   <si>
     <t>JESICA ROSHIMA</t>
@@ -2431,7 +2431,7 @@
     <t>Vit51348@123</t>
   </si>
   <si>
-    <t>(multi)51352</t>
+    <t>(MULTI)51352</t>
   </si>
   <si>
     <t>DHIVYA M</t>
@@ -2443,7 +2443,7 @@
     <t>Vit51352@123</t>
   </si>
   <si>
-    <t>(multi)51448</t>
+    <t>(MULTI)51448</t>
   </si>
   <si>
     <t>VASANTH KUMAR</t>
@@ -2455,7 +2455,7 @@
     <t>Vit51448@123</t>
   </si>
   <si>
-    <t>(multi)51450</t>
+    <t>(MULTI)51450</t>
   </si>
   <si>
     <t>VIJAYARAJAN R</t>
@@ -2467,7 +2467,7 @@
     <t>Vit51450@123</t>
   </si>
   <si>
-    <t>(multi)51454</t>
+    <t>(MULTI)51454</t>
   </si>
   <si>
     <t>KIRAN KUMAR TADI</t>
@@ -2479,7 +2479,7 @@
     <t>Vit51454@123</t>
   </si>
   <si>
-    <t>(multi)51457</t>
+    <t>(MULTI)51457</t>
   </si>
   <si>
     <t>MANAS RANJAN PRUSTY</t>
@@ -2491,7 +2491,7 @@
     <t>Vit51457@123</t>
   </si>
   <si>
-    <t>(multi)51458</t>
+    <t>(MULTI)51458</t>
   </si>
   <si>
     <t>R JOTHI</t>
@@ -2503,7 +2503,7 @@
     <t>Vit51458@123</t>
   </si>
   <si>
-    <t>(multi)51459</t>
+    <t>(MULTI)51459</t>
   </si>
   <si>
     <t>INAYATHULLAAH ABDUL KAREEM</t>
@@ -2515,7 +2515,7 @@
     <t>Vit51459@123</t>
   </si>
   <si>
-    <t>(multi)51464</t>
+    <t>(MULTI)51464</t>
   </si>
   <si>
     <t>BUTHANAPALLI RAMAKRISHNA</t>
@@ -2527,7 +2527,7 @@
     <t>Vit51464@123</t>
   </si>
   <si>
-    <t>(multi)51465</t>
+    <t>(MULTI)51465</t>
   </si>
   <si>
     <t>ILAIYARAJA PERUMAL</t>
@@ -2539,7 +2539,7 @@
     <t>Vit51465@123</t>
   </si>
   <si>
-    <t>(multi)51651</t>
+    <t>(MULTI)51651</t>
   </si>
   <si>
     <t>MUTHUKUMARAN K</t>
@@ -2551,7 +2551,7 @@
     <t>Vit51651@123</t>
   </si>
   <si>
-    <t>(multi)51652</t>
+    <t>(MULTI)51652</t>
   </si>
   <si>
     <t>VENKATRAMAN S</t>
@@ -2563,7 +2563,7 @@
     <t>Vit51652@123</t>
   </si>
   <si>
-    <t>(multi)51658</t>
+    <t>(MULTI)51658</t>
   </si>
   <si>
     <t>PARKAVI K</t>
@@ -2575,7 +2575,7 @@
     <t>Vit51658@123</t>
   </si>
   <si>
-    <t>(multi)51659</t>
+    <t>(MULTI)51659</t>
   </si>
   <si>
     <t>SHIVANI GUPTA</t>
@@ -2587,7 +2587,7 @@
     <t>Vit51659@123</t>
   </si>
   <si>
-    <t>(multi)51663</t>
+    <t>(MULTI)51663</t>
   </si>
   <si>
     <t>SUBBULAKSHMI P</t>
@@ -2599,7 +2599,7 @@
     <t>Vit51663@123</t>
   </si>
   <si>
-    <t>(multi)51665</t>
+    <t>(MULTI)51665</t>
   </si>
   <si>
     <t>AMRIT PAL</t>
@@ -2611,7 +2611,7 @@
     <t>Vit51665@123</t>
   </si>
   <si>
-    <t>(multi)51667</t>
+    <t>(MULTI)51667</t>
   </si>
   <si>
     <t>LENINISHA SHANMUGAM</t>
@@ -2623,7 +2623,7 @@
     <t>Vit51667@123</t>
   </si>
   <si>
-    <t>(multi)51669</t>
+    <t>(MULTI)51669</t>
   </si>
   <si>
     <t>A SWAMINATHAN</t>
@@ -2635,7 +2635,7 @@
     <t>Vit51669@123</t>
   </si>
   <si>
-    <t>(multi)51672</t>
+    <t>(MULTI)51672</t>
   </si>
   <si>
     <t>RISHIKESHAN C A</t>
@@ -2647,7 +2647,7 @@
     <t>Vit51672@123</t>
   </si>
   <si>
-    <t>(multi)51679</t>
+    <t>(MULTI)51679</t>
   </si>
   <si>
     <t>GANALA SANTOSHI</t>
@@ -2659,7 +2659,7 @@
     <t>Vit51679@123</t>
   </si>
   <si>
-    <t>(multi)51682</t>
+    <t>(MULTI)51682</t>
   </si>
   <si>
     <t>PRAKASH P</t>
@@ -2671,7 +2671,7 @@
     <t>Vit51682@123</t>
   </si>
   <si>
-    <t>(multi)51683</t>
+    <t>(MULTI)51683</t>
   </si>
   <si>
     <t>SUDIP DEBNATH</t>
@@ -2683,7 +2683,7 @@
     <t>Vit51683@123</t>
   </si>
   <si>
-    <t>(multi)51684</t>
+    <t>(MULTI)51684</t>
   </si>
   <si>
     <t>DURGAPRASAD P</t>
@@ -2695,7 +2695,7 @@
     <t>Vit51684@123</t>
   </si>
   <si>
-    <t>(multi)51686</t>
+    <t>(MULTI)51686</t>
   </si>
   <si>
     <t>SOMNATH BERA</t>
@@ -2707,7 +2707,7 @@
     <t>Vit51686@123</t>
   </si>
   <si>
-    <t>(multi)51687</t>
+    <t>(MULTI)51687</t>
   </si>
   <si>
     <t>AJITHA B</t>
@@ -2719,7 +2719,7 @@
     <t>Vit51687@123</t>
   </si>
   <si>
-    <t>(multi)51695</t>
+    <t>(MULTI)51695</t>
   </si>
   <si>
     <t>VIJAY KUMAR P</t>
@@ -2731,7 +2731,7 @@
     <t>Vit51695@123</t>
   </si>
   <si>
-    <t>(multi)51697</t>
+    <t>(MULTI)51697</t>
   </si>
   <si>
     <t>ARIVARASI A</t>
@@ -2743,7 +2743,7 @@
     <t>Vit51697@123</t>
   </si>
   <si>
-    <t>(multi)51699</t>
+    <t>(MULTI)51699</t>
   </si>
   <si>
     <t>PAPANASAM E</t>
@@ -2755,7 +2755,7 @@
     <t>Vit51699@123</t>
   </si>
   <si>
-    <t>(multi)51700</t>
+    <t>(MULTI)51700</t>
   </si>
   <si>
     <t>SATHYA SREE J</t>
@@ -2767,7 +2767,7 @@
     <t>Vit51700@123</t>
   </si>
   <si>
-    <t>(multi)51703</t>
+    <t>(MULTI)51703</t>
   </si>
   <si>
     <t>B PRASHANTH KUMAR</t>
@@ -2779,7 +2779,7 @@
     <t>Vit51703@123</t>
   </si>
   <si>
-    <t>(multi)51707</t>
+    <t>(MULTI)51707</t>
   </si>
   <si>
     <t>CHANTHINI BASKAR</t>
@@ -2791,7 +2791,7 @@
     <t>Vit51707@123</t>
   </si>
   <si>
-    <t>(multi)51708</t>
+    <t>(MULTI)51708</t>
   </si>
   <si>
     <t>S SIVAKUMAR</t>
@@ -2803,7 +2803,7 @@
     <t>Vit51708@123</t>
   </si>
   <si>
-    <t>(multi)51709</t>
+    <t>(MULTI)51709</t>
   </si>
   <si>
     <t>E MANIKANDAN</t>
@@ -2815,7 +2815,7 @@
     <t>Vit51709@123</t>
   </si>
   <si>
-    <t>(multi)51710</t>
+    <t>(MULTI)51710</t>
   </si>
   <si>
     <t>S SELVENDRAN</t>
@@ -2827,7 +2827,7 @@
     <t>Vit51710@123</t>
   </si>
   <si>
-    <t>(multi)51712</t>
+    <t>(MULTI)51712</t>
   </si>
   <si>
     <t>G LAKSHMI PRIYA</t>
@@ -2839,7 +2839,7 @@
     <t>Vit51712@123</t>
   </si>
   <si>
-    <t>(multi)51713</t>
+    <t>(MULTI)51713</t>
   </si>
   <si>
     <t>JEETASHREE APARAJEETA</t>
@@ -2851,7 +2851,7 @@
     <t>Vit51713@123</t>
   </si>
   <si>
-    <t>(multi)51714</t>
+    <t>(MULTI)51714</t>
   </si>
   <si>
     <t>KALAIVANAN K</t>
@@ -2863,7 +2863,7 @@
     <t>Vit51714@123</t>
   </si>
   <si>
-    <t>(multi)51715</t>
+    <t>(MULTI)51715</t>
   </si>
   <si>
     <t>P NIRMALA</t>
@@ -2875,7 +2875,7 @@
     <t>Vit51715@123</t>
   </si>
   <si>
-    <t>(multi)51716</t>
+    <t>(MULTI)51716</t>
   </si>
   <si>
     <t>S SHOBA</t>
@@ -2887,7 +2887,7 @@
     <t>Vit51716@123</t>
   </si>
   <si>
-    <t>(multi)51717</t>
+    <t>(MULTI)51717</t>
   </si>
   <si>
     <t>SINDHUJA M</t>
@@ -2899,7 +2899,7 @@
     <t>Vit51717@123</t>
   </si>
   <si>
-    <t>(multi)51718</t>
+    <t>(MULTI)51718</t>
   </si>
   <si>
     <t>A BHARATHI SANKAR</t>
@@ -2911,7 +2911,7 @@
     <t>Vit51718@123</t>
   </si>
   <si>
-    <t>(multi)51720</t>
+    <t>(MULTI)51720</t>
   </si>
   <si>
     <t>IDAYACHANDRAN G</t>
@@ -2923,7 +2923,7 @@
     <t>Vit51720@123</t>
   </si>
   <si>
-    <t>(multi)51721</t>
+    <t>(MULTI)51721</t>
   </si>
   <si>
     <t>RANJEET KUMAR</t>
@@ -2935,7 +2935,7 @@
     <t>Vit51721@123</t>
   </si>
   <si>
-    <t>(multi)51722</t>
+    <t>(MULTI)51722</t>
   </si>
   <si>
     <t>BHISHAM KUMAR DHURANDHER</t>
@@ -2947,7 +2947,7 @@
     <t>Vit51722@123</t>
   </si>
   <si>
-    <t>(multi)51723</t>
+    <t>(MULTI)51723</t>
   </si>
   <si>
     <t>(multi)r.manojkumar@vit.ac.in</t>
@@ -2956,7 +2956,7 @@
     <t>Vit51723@123</t>
   </si>
   <si>
-    <t>(multi)51724</t>
+    <t>(MULTI)51724</t>
   </si>
   <si>
     <t>GAJANAND GUPTA</t>
@@ -2968,7 +2968,7 @@
     <t>Vit51724@123</t>
   </si>
   <si>
-    <t>(multi)51725</t>
+    <t>(MULTI)51725</t>
   </si>
   <si>
     <t>AWANI BHUSHAN</t>
@@ -2980,7 +2980,7 @@
     <t>Vit51725@123</t>
   </si>
   <si>
-    <t>(multi)51726</t>
+    <t>(MULTI)51726</t>
   </si>
   <si>
     <t>MRUTYUNJAY PANIGRAHI</t>
@@ -2992,7 +2992,7 @@
     <t>Vit51726@123</t>
   </si>
   <si>
-    <t>(multi)51727</t>
+    <t>(MULTI)51727</t>
   </si>
   <si>
     <t>G MURALIMOHAN</t>
@@ -3004,7 +3004,7 @@
     <t>Vit51727@123</t>
   </si>
   <si>
-    <t>(multi)51729</t>
+    <t>(MULTI)51729</t>
   </si>
   <si>
     <t>AYUB AHMED JANVEKAR</t>
@@ -3016,7 +3016,7 @@
     <t>Vit51729@123</t>
   </si>
   <si>
-    <t>(multi)51743</t>
+    <t>(MULTI)51743</t>
   </si>
   <si>
     <t>VIJAYAKUMAR K P</t>
@@ -3028,7 +3028,7 @@
     <t>Vit51743@123</t>
   </si>
   <si>
-    <t>(multi)51744</t>
+    <t>(MULTI)51744</t>
   </si>
   <si>
     <t>SAURAV GUPTA</t>
@@ -3040,7 +3040,7 @@
     <t>Vit51744@123</t>
   </si>
   <si>
-    <t>(multi)51747</t>
+    <t>(MULTI)51747</t>
   </si>
   <si>
     <t>TAPAN KUMAR MAHANTA</t>
@@ -3052,7 +3052,7 @@
     <t>Vit51747@123</t>
   </si>
   <si>
-    <t>(multi)51748</t>
+    <t>(MULTI)51748</t>
   </si>
   <si>
     <t>PRADEEP K</t>
@@ -3064,7 +3064,7 @@
     <t>Vit51748@123</t>
   </si>
   <si>
-    <t>(multi)51749</t>
+    <t>(MULTI)51749</t>
   </si>
   <si>
     <t>RICHARDS JOE STANISLAUS</t>
@@ -3076,7 +3076,7 @@
     <t>Vit51749@123</t>
   </si>
   <si>
-    <t>(multi)51751</t>
+    <t>(MULTI)51751</t>
   </si>
   <si>
     <t>V.R BALAJI</t>
@@ -3088,7 +3088,7 @@
     <t>Vit51751@123</t>
   </si>
   <si>
-    <t>(multi)51752</t>
+    <t>(MULTI)51752</t>
   </si>
   <si>
     <t>SASITHRADEVI. A</t>
@@ -3100,7 +3100,7 @@
     <t>Vit51752@123</t>
   </si>
   <si>
-    <t>(multi)51754</t>
+    <t>(MULTI)51754</t>
   </si>
   <si>
     <t>RADHA R</t>
@@ -3112,7 +3112,7 @@
     <t>Vit51754@123</t>
   </si>
   <si>
-    <t>(multi)51766</t>
+    <t>(MULTI)51766</t>
   </si>
   <si>
     <t>R. D. EITHIRAJ</t>
@@ -3124,7 +3124,7 @@
     <t>Vit51766@123</t>
   </si>
   <si>
-    <t>(multi)51939</t>
+    <t>(MULTI)51939</t>
   </si>
   <si>
     <t>GANESAN</t>
@@ -3136,7 +3136,7 @@
     <t>Vit51939@123</t>
   </si>
   <si>
-    <t>(multi)51940</t>
+    <t>(MULTI)51940</t>
   </si>
   <si>
     <t>RAMACHANDRAN</t>
@@ -3148,7 +3148,7 @@
     <t>Vit51940@123</t>
   </si>
   <si>
-    <t>(multi)51941</t>
+    <t>(MULTI)51941</t>
   </si>
   <si>
     <t>SUJOY SARKAR</t>
@@ -3160,7 +3160,7 @@
     <t>Vit51941@123</t>
   </si>
   <si>
-    <t>(multi)51943</t>
+    <t>(MULTI)51943</t>
   </si>
   <si>
     <t>DURGA</t>
@@ -3172,7 +3172,7 @@
     <t>Vit51943@123</t>
   </si>
   <si>
-    <t>(multi)51946</t>
+    <t>(MULTI)51946</t>
   </si>
   <si>
     <t>KALAIPRIYAN</t>
@@ -3184,7 +3184,7 @@
     <t>Vit51946@123</t>
   </si>
   <si>
-    <t>(multi)51947</t>
+    <t>(MULTI)51947</t>
   </si>
   <si>
     <t>RAJAKUMAR ARUL</t>
@@ -3196,7 +3196,7 @@
     <t>Vit51947@123</t>
   </si>
   <si>
-    <t>(multi)51948</t>
+    <t>(MULTI)51948</t>
   </si>
   <si>
     <t>SUDHA</t>
@@ -3208,7 +3208,7 @@
     <t>Vit51948@123</t>
   </si>
   <si>
-    <t>(multi)51949</t>
+    <t>(MULTI)51949</t>
   </si>
   <si>
     <t>SUGANESHWARI</t>
@@ -3220,7 +3220,7 @@
     <t>Vit51949@123</t>
   </si>
   <si>
-    <t>(multi)51962</t>
+    <t>(MULTI)51962</t>
   </si>
   <si>
     <t>SHRUTI MISHRA</t>
@@ -3232,7 +3232,7 @@
     <t>Vit51962@123</t>
   </si>
   <si>
-    <t>(multi)51964</t>
+    <t>(MULTI)51964</t>
   </si>
   <si>
     <t>BALAJI</t>
@@ -3244,7 +3244,7 @@
     <t>Vit51964@123</t>
   </si>
   <si>
-    <t>(multi)51973</t>
+    <t>(MULTI)51973</t>
   </si>
   <si>
     <t>BHUVANESHWARI</t>
@@ -3256,7 +3256,7 @@
     <t>Vit51973@123</t>
   </si>
   <si>
-    <t>(multi)51974</t>
+    <t>(MULTI)51974</t>
   </si>
   <si>
     <t>AROCKIASAMY</t>
@@ -3268,7 +3268,7 @@
     <t>Vit51974@123</t>
   </si>
   <si>
-    <t>(multi)52055</t>
+    <t>(MULTI)52055</t>
   </si>
   <si>
     <t>RAJASEKARAKUMAR V</t>
@@ -3280,7 +3280,7 @@
     <t>Vit52055@123</t>
   </si>
   <si>
-    <t>(multi)52192</t>
+    <t>(MULTI)52192</t>
   </si>
   <si>
     <t>VALARMATHI SUDHAKAR</t>
@@ -3292,7 +3292,7 @@
     <t>Vit52192@123</t>
   </si>
   <si>
-    <t>(multi)52193</t>
+    <t>(MULTI)52193</t>
   </si>
   <si>
     <t>N G BHUVANESWARI</t>
@@ -3304,7 +3304,7 @@
     <t>Vit52193@123</t>
   </si>
   <si>
-    <t>(multi)52194</t>
+    <t>(MULTI)52194</t>
   </si>
   <si>
     <t>ABISHI CHOWDHURY</t>
@@ -3316,7 +3316,7 @@
     <t>Vit52194@123</t>
   </si>
   <si>
-    <t>(multi)52199</t>
+    <t>(MULTI)52199</t>
   </si>
   <si>
     <t>KRISHNA KUMAR</t>
@@ -3328,7 +3328,7 @@
     <t>Vit52199@123</t>
   </si>
   <si>
-    <t>(multi)52201</t>
+    <t>(MULTI)52201</t>
   </si>
   <si>
     <t>RAJIVGANTHI</t>
@@ -3340,7 +3340,7 @@
     <t>Vit52201@123</t>
   </si>
   <si>
-    <t>(multi)52203</t>
+    <t>(MULTI)52203</t>
   </si>
   <si>
     <t>HARSHAVARTHINI</t>
@@ -3352,7 +3352,7 @@
     <t>Vit52203@123</t>
   </si>
   <si>
-    <t>(multi)52204</t>
+    <t>(MULTI)52204</t>
   </si>
   <si>
     <t>MANIMEGALAI</t>
@@ -3364,7 +3364,7 @@
     <t>Vit52204@123</t>
   </si>
   <si>
-    <t>(multi)52205</t>
+    <t>(MULTI)52205</t>
   </si>
   <si>
     <t>RAMKUMAR</t>
@@ -3376,7 +3376,7 @@
     <t>Vit52205@123</t>
   </si>
   <si>
-    <t>(multi)52207</t>
+    <t>(MULTI)52207</t>
   </si>
   <si>
     <t>KIRUTHIKA</t>
@@ -3388,7 +3388,7 @@
     <t>Vit52207@123</t>
   </si>
   <si>
-    <t>(multi)52208</t>
+    <t>(MULTI)52208</t>
   </si>
   <si>
     <t>INDRA PRIYADHARSHINI</t>
@@ -3400,7 +3400,7 @@
     <t>Vit52208@123</t>
   </si>
   <si>
-    <t>(multi)52209</t>
+    <t>(MULTI)52209</t>
   </si>
   <si>
     <t>KAVITHA</t>
@@ -3412,7 +3412,7 @@
     <t>Vit52209@123</t>
   </si>
   <si>
-    <t>(multi)52210</t>
+    <t>(MULTI)52210</t>
   </si>
   <si>
     <t>RAVI TIWARI</t>
@@ -3424,7 +3424,7 @@
     <t>Vit52210@123</t>
   </si>
   <si>
-    <t>(multi)52215</t>
+    <t>(MULTI)52215</t>
   </si>
   <si>
     <t>SUGUNA</t>
@@ -3436,7 +3436,7 @@
     <t>Vit52215@123</t>
   </si>
   <si>
-    <t>(multi)52224</t>
+    <t>(MULTI)52224</t>
   </si>
   <si>
     <t>SOURABH PAUL</t>
@@ -3448,7 +3448,7 @@
     <t>Vit52224@123</t>
   </si>
   <si>
-    <t>(multi)52227</t>
+    <t>(MULTI)52227</t>
   </si>
   <si>
     <t>SHERLY A</t>
@@ -3460,7 +3460,7 @@
     <t>Vit52227@123</t>
   </si>
   <si>
-    <t>(multi)52232</t>
+    <t>(MULTI)52232</t>
   </si>
   <si>
     <t>ABINAYA S</t>
@@ -3472,7 +3472,7 @@
     <t>Vit52232@123</t>
   </si>
   <si>
-    <t>(multi)52233</t>
+    <t>(MULTI)52233</t>
   </si>
   <si>
     <t>THARASI DILLESWAR</t>
@@ -3484,7 +3484,7 @@
     <t>Vit52233@123</t>
   </si>
   <si>
-    <t>(multi)52235</t>
+    <t>(MULTI)52235</t>
   </si>
   <si>
     <t>ASHISH KUMAR</t>
@@ -3496,7 +3496,7 @@
     <t>Vit52235@123</t>
   </si>
   <si>
-    <t>(multi)52236</t>
+    <t>(MULTI)52236</t>
   </si>
   <si>
     <t>KALYAN</t>
@@ -3508,7 +3508,7 @@
     <t>Vit52236@123</t>
   </si>
   <si>
-    <t>(multi)52237</t>
+    <t>(MULTI)52237</t>
   </si>
   <si>
     <t>PROSENJIT</t>
@@ -3520,7 +3520,7 @@
     <t>Vit52237@123</t>
   </si>
   <si>
-    <t>(multi)52238</t>
+    <t>(MULTI)52238</t>
   </si>
   <si>
     <t>DHIVYA P</t>
@@ -3532,7 +3532,7 @@
     <t>Vit52238@123</t>
   </si>
   <si>
-    <t>(multi)52239</t>
+    <t>(MULTI)52239</t>
   </si>
   <si>
     <t>PADMAVATHY T V</t>
@@ -3544,7 +3544,7 @@
     <t>Vit52239@123</t>
   </si>
   <si>
-    <t>(multi)52244</t>
+    <t>(MULTI)52244</t>
   </si>
   <si>
     <t>LOGESH R</t>
@@ -3556,7 +3556,7 @@
     <t>Vit52244@123</t>
   </si>
   <si>
-    <t>(multi)52245</t>
+    <t>(MULTI)52245</t>
   </si>
   <si>
     <t>SAHAYA BENI PRATHIBA B</t>
@@ -3568,7 +3568,7 @@
     <t>Vit52245@123</t>
   </si>
   <si>
-    <t>(multi)52247</t>
+    <t>(MULTI)52247</t>
   </si>
   <si>
     <t>TAMILARASI K</t>
@@ -3580,7 +3580,7 @@
     <t>Vit52247@123</t>
   </si>
   <si>
-    <t>(multi)52252</t>
+    <t>(MULTI)52252</t>
   </si>
   <si>
     <t>PRITAM DAS</t>
@@ -3592,7 +3592,7 @@
     <t>Vit52252@123</t>
   </si>
   <si>
-    <t>(multi)52253</t>
+    <t>(MULTI)52253</t>
   </si>
   <si>
     <t>SAURABH CHANDRA MAURY</t>
@@ -3604,7 +3604,7 @@
     <t>Vit52253@123</t>
   </si>
   <si>
-    <t>(multi)52256</t>
+    <t>(MULTI)52256</t>
   </si>
   <si>
     <t>SATHIAN D</t>
@@ -3616,7 +3616,7 @@
     <t>Vit52256@123</t>
   </si>
   <si>
-    <t>(multi)52257</t>
+    <t>(MULTI)52257</t>
   </si>
   <si>
     <t>KARTHIKEYAN S</t>
@@ -3628,7 +3628,7 @@
     <t>Vit52257@123</t>
   </si>
   <si>
-    <t>(multi)52258</t>
+    <t>(MULTI)52258</t>
   </si>
   <si>
     <t>PAVITHRA R</t>
@@ -3640,7 +3640,7 @@
     <t>Vit52258@123</t>
   </si>
   <si>
-    <t>(multi)52261</t>
+    <t>(MULTI)52261</t>
   </si>
   <si>
     <t>BHAVADHARINI R M</t>
@@ -3652,7 +3652,7 @@
     <t>Vit52261@123</t>
   </si>
   <si>
-    <t>(multi)52262</t>
+    <t>(MULTI)52262</t>
   </si>
   <si>
     <t>MERCY RAJASELVI BEAULAH P</t>
@@ -3664,7 +3664,7 @@
     <t>Vit52262@123</t>
   </si>
   <si>
-    <t>(multi)52263</t>
+    <t>(MULTI)52263</t>
   </si>
   <si>
     <t>OM KUMAR C U</t>
@@ -3676,7 +3676,7 @@
     <t>Vit52263@123</t>
   </si>
   <si>
-    <t>(multi)52264</t>
+    <t>(MULTI)52264</t>
   </si>
   <si>
     <t>KRITHIGA R</t>
@@ -3688,7 +3688,7 @@
     <t>Vit52264@123</t>
   </si>
   <si>
-    <t>(multi)52265</t>
+    <t>(MULTI)52265</t>
   </si>
   <si>
     <t>ASHIS BERA</t>
@@ -3700,7 +3700,7 @@
     <t>Vit52265@123</t>
   </si>
   <si>
-    <t>(multi)52266</t>
+    <t>(MULTI)52266</t>
   </si>
   <si>
     <t>SUSEELA S</t>
@@ -3712,7 +3712,7 @@
     <t>Vit52266@123</t>
   </si>
   <si>
-    <t>(multi)52267</t>
+    <t>(MULTI)52267</t>
   </si>
   <si>
     <t>ROHITH G</t>
@@ -3724,7 +3724,7 @@
     <t>Vit52267@123</t>
   </si>
   <si>
-    <t>(multi)52268</t>
+    <t>(MULTI)52268</t>
   </si>
   <si>
     <t>SUNIL KUMAR PRADHAN</t>
@@ -3736,7 +3736,7 @@
     <t>Vit52268@123</t>
   </si>
   <si>
-    <t>(multi)52269</t>
+    <t>(MULTI)52269</t>
   </si>
   <si>
     <t>LAKSHMANAN S</t>
@@ -3748,7 +3748,7 @@
     <t>Vit52269@123</t>
   </si>
   <si>
-    <t>(multi)52270</t>
+    <t>(MULTI)52270</t>
   </si>
   <si>
     <t>ANKIT KUMAR</t>
@@ -3760,7 +3760,7 @@
     <t>Vit52270@123</t>
   </si>
   <si>
-    <t>(multi)52271</t>
+    <t>(MULTI)52271</t>
   </si>
   <si>
     <t>OM NAMHA SHIVAY</t>
@@ -3772,7 +3772,7 @@
     <t>Vit52271@123</t>
   </si>
   <si>
-    <t>(multi)52273</t>
+    <t>(MULTI)52273</t>
   </si>
   <si>
     <t>S A AMUTHA JEEVAKUMARI</t>
@@ -3784,7 +3784,7 @@
     <t>Vit52273@123</t>
   </si>
   <si>
-    <t>(multi)52275</t>
+    <t>(MULTI)52275</t>
   </si>
   <si>
     <t>NOEL JEYGAR ROBERT V</t>
@@ -3796,7 +3796,7 @@
     <t>Vit52275@123</t>
   </si>
   <si>
-    <t>(multi)52276</t>
+    <t>(MULTI)52276</t>
   </si>
   <si>
     <t>JUSTIN RAJ</t>
@@ -3808,7 +3808,7 @@
     <t>Vit52276@123</t>
   </si>
   <si>
-    <t>(multi)52277</t>
+    <t>(MULTI)52277</t>
   </si>
   <si>
     <t>ARUNKUMAR</t>
@@ -3820,7 +3820,7 @@
     <t>Vit52277@123</t>
   </si>
   <si>
-    <t>(multi)52278</t>
+    <t>(MULTI)52278</t>
   </si>
   <si>
     <t>MANJULA V</t>
@@ -3832,7 +3832,7 @@
     <t>Vit52278@123</t>
   </si>
   <si>
-    <t>(multi)52279</t>
+    <t>(MULTI)52279</t>
   </si>
   <si>
     <t>RAMA PRABHA</t>
@@ -3844,7 +3844,7 @@
     <t>Vit52279@123</t>
   </si>
   <si>
-    <t>(multi)52280</t>
+    <t>(MULTI)52280</t>
   </si>
   <si>
     <t>UMA MAHESWARI</t>
@@ -3856,7 +3856,7 @@
     <t>Vit52280@123</t>
   </si>
   <si>
-    <t>(multi)52281</t>
+    <t>(MULTI)52281</t>
   </si>
   <si>
     <t>SIVAKUMAR</t>
@@ -3868,7 +3868,7 @@
     <t>Vit52281@123</t>
   </si>
   <si>
-    <t>(multi)52283</t>
+    <t>(MULTI)52283</t>
   </si>
   <si>
     <t>MONICA</t>
@@ -3880,7 +3880,7 @@
     <t>Vit52283@123</t>
   </si>
   <si>
-    <t>(multi)52284</t>
+    <t>(MULTI)52284</t>
   </si>
   <si>
     <t>BRINDHA</t>
@@ -3892,7 +3892,7 @@
     <t>Vit52284@123</t>
   </si>
   <si>
-    <t>(multi)52285</t>
+    <t>(MULTI)52285</t>
   </si>
   <si>
     <t>SANDOSH</t>
@@ -3904,7 +3904,7 @@
     <t>Vit52285@123</t>
   </si>
   <si>
-    <t>(multi)52288</t>
+    <t>(MULTI)52288</t>
   </si>
   <si>
     <t>RENJITH</t>
@@ -3916,7 +3916,7 @@
     <t>Vit52288@123</t>
   </si>
   <si>
-    <t>(multi)52289</t>
+    <t>(MULTI)52289</t>
   </si>
   <si>
     <t>SURATH</t>
@@ -3928,7 +3928,7 @@
     <t>Vit52289@123</t>
   </si>
   <si>
-    <t>(multi)52291</t>
+    <t>(MULTI)52291</t>
   </si>
   <si>
     <t>ASWIGA</t>
@@ -3940,7 +3940,7 @@
     <t>Vit52291@123</t>
   </si>
   <si>
-    <t>(multi)52292</t>
+    <t>(MULTI)52292</t>
   </si>
   <si>
     <t>HARIHARAN</t>
@@ -3952,7 +3952,7 @@
     <t>Vit52292@123</t>
   </si>
   <si>
-    <t>(multi)52293</t>
+    <t>(MULTI)52293</t>
   </si>
   <si>
     <t>SANDIP</t>
@@ -3964,7 +3964,7 @@
     <t>Vit52293@123</t>
   </si>
   <si>
-    <t>(multi)52294</t>
+    <t>(MULTI)52294</t>
   </si>
   <si>
     <t>MANIMARAN P</t>
@@ -3976,7 +3976,7 @@
     <t>Vit52294@123</t>
   </si>
   <si>
-    <t>(multi)52295</t>
+    <t>(MULTI)52295</t>
   </si>
   <si>
     <t>JOSHAN</t>
@@ -3988,7 +3988,7 @@
     <t>Vit52295@123</t>
   </si>
   <si>
-    <t>(multi)52297</t>
+    <t>(MULTI)52297</t>
   </si>
   <si>
     <t>ASHIS TRIPATHY</t>
@@ -4000,7 +4000,7 @@
     <t>Vit52297@123</t>
   </si>
   <si>
-    <t>(multi)52298</t>
+    <t>(MULTI)52298</t>
   </si>
   <si>
     <t>GIRIJA SHANKAR SAHOO</t>
@@ -4012,7 +4012,7 @@
     <t>Vit52298@123</t>
   </si>
   <si>
-    <t>(multi)52299</t>
+    <t>(MULTI)52299</t>
   </si>
   <si>
     <t>JOE DHANITH</t>
@@ -4024,7 +4024,7 @@
     <t>Vit52299@123</t>
   </si>
   <si>
-    <t>(multi)52301</t>
+    <t>(MULTI)52301</t>
   </si>
   <si>
     <t>SUDHAKARAN</t>
@@ -4036,7 +4036,7 @@
     <t>Vit52301@123</t>
   </si>
   <si>
-    <t>(multi)52303</t>
+    <t>(MULTI)52303</t>
   </si>
   <si>
     <t>REENA ROY R</t>
@@ -4048,7 +4048,7 @@
     <t>Vit52303@123</t>
   </si>
   <si>
-    <t>(multi)52304</t>
+    <t>(MULTI)52304</t>
   </si>
   <si>
     <t>SURESHKUMAR WI</t>
@@ -4060,7 +4060,7 @@
     <t>Vit52304@123</t>
   </si>
   <si>
-    <t>(multi)52305</t>
+    <t>(MULTI)52305</t>
   </si>
   <si>
     <t>MARKKANDAN</t>
@@ -4072,7 +4072,7 @@
     <t>Vit52305@123</t>
   </si>
   <si>
-    <t>(multi)52306</t>
+    <t>(MULTI)52306</t>
   </si>
   <si>
     <t>PRITAM</t>
@@ -4084,7 +4084,7 @@
     <t>Vit52306@123</t>
   </si>
   <si>
-    <t>(multi)52307</t>
+    <t>(MULTI)52307</t>
   </si>
   <si>
     <t>ABHISHEK</t>
@@ -4096,7 +4096,7 @@
     <t>Vit52307@123</t>
   </si>
   <si>
-    <t>(multi)52309</t>
+    <t>(MULTI)52309</t>
   </si>
   <si>
     <t>SMRITHY</t>
@@ -4108,7 +4108,7 @@
     <t>Vit52309@123</t>
   </si>
   <si>
-    <t>(multi)52310</t>
+    <t>(MULTI)52310</t>
   </si>
   <si>
     <t>MARIA ANU</t>
@@ -4120,7 +4120,7 @@
     <t>Vit52310@123</t>
   </si>
   <si>
-    <t>(multi)52312</t>
+    <t>(MULTI)52312</t>
   </si>
   <si>
     <t>(multi)kiruthika.s@vit.ac.in</t>
@@ -4129,7 +4129,7 @@
     <t>Vit52312@123</t>
   </si>
   <si>
-    <t>(multi)52315</t>
+    <t>(MULTI)52315</t>
   </si>
   <si>
     <t>SETHUKUMARASAMY</t>
@@ -4141,7 +4141,7 @@
     <t>Vit52315@123</t>
   </si>
   <si>
-    <t>(multi)52316</t>
+    <t>(MULTI)52316</t>
   </si>
   <si>
     <t>ASHOK</t>
@@ -4153,7 +4153,7 @@
     <t>Vit52316@123</t>
   </si>
   <si>
-    <t>(multi)52318</t>
+    <t>(MULTI)52318</t>
   </si>
   <si>
     <t>AMIT KUMAR RAHUL</t>
@@ -4165,7 +4165,7 @@
     <t>Vit52318@123</t>
   </si>
   <si>
-    <t>(multi)52320</t>
+    <t>(MULTI)52320</t>
   </si>
   <si>
     <t>RAHUL NARASIMHAN</t>
@@ -4177,7 +4177,7 @@
     <t>Vit52320@123</t>
   </si>
   <si>
-    <t>(multi)52321</t>
+    <t>(MULTI)52321</t>
   </si>
   <si>
     <t>BISWAJIT</t>
@@ -4189,7 +4189,7 @@
     <t>Vit52321@123</t>
   </si>
   <si>
-    <t>(multi)52322</t>
+    <t>(MULTI)52322</t>
   </si>
   <si>
     <t>MODIGARI NARENDRA</t>
@@ -4201,7 +4201,7 @@
     <t>Vit52322@123</t>
   </si>
   <si>
-    <t>(multi)52324</t>
+    <t>(MULTI)52324</t>
   </si>
   <si>
     <t>SAURABH YADAV</t>
@@ -4213,7 +4213,7 @@
     <t>Vit52324@123</t>
   </si>
   <si>
-    <t>(multi)52334</t>
+    <t>(MULTI)52334</t>
   </si>
   <si>
     <t>SANGEETHA N</t>
@@ -4225,7 +4225,7 @@
     <t>Vit52334@123</t>
   </si>
   <si>
-    <t>(multi)52337</t>
+    <t>(MULTI)52337</t>
   </si>
   <si>
     <t>ANANDAN P</t>
@@ -4237,7 +4237,7 @@
     <t>Vit52337@123</t>
   </si>
   <si>
-    <t>(multi)52338</t>
+    <t>(MULTI)52338</t>
   </si>
   <si>
     <t>D JEYA MALA</t>
@@ -4249,7 +4249,7 @@
     <t>Vit52338@123</t>
   </si>
   <si>
-    <t>(multi)52339</t>
+    <t>(MULTI)52339</t>
   </si>
   <si>
     <t>DHEEREN KU MAHAPATRA</t>
@@ -4261,7 +4261,7 @@
     <t>Vit52339@123</t>
   </si>
   <si>
-    <t>(multi)52341</t>
+    <t>(MULTI)52341</t>
   </si>
   <si>
     <t>PRAVEEN JOE I R</t>
@@ -4273,7 +4273,7 @@
     <t>Vit52341@123</t>
   </si>
   <si>
-    <t>(multi)52342</t>
+    <t>(MULTI)52342</t>
   </si>
   <si>
     <t>SARASWATHI D</t>
@@ -4285,7 +4285,7 @@
     <t>Vit52342@123</t>
   </si>
   <si>
-    <t>(multi)52343</t>
+    <t>(MULTI)52343</t>
   </si>
   <si>
     <t>DINAKARAN M</t>
@@ -4297,7 +4297,7 @@
     <t>Vit52343@123</t>
   </si>
   <si>
-    <t>(multi)52344</t>
+    <t>(MULTI)52344</t>
   </si>
   <si>
     <t>PANDIYARAJU V</t>
@@ -4309,7 +4309,7 @@
     <t>Vit52344@123</t>
   </si>
   <si>
-    <t>(multi)52346</t>
+    <t>(MULTI)52346</t>
   </si>
   <si>
     <t>MARY SHAMALA L</t>
@@ -4321,7 +4321,7 @@
     <t>Vit52346@123</t>
   </si>
   <si>
-    <t>(multi)52347</t>
+    <t>(MULTI)52347</t>
   </si>
   <si>
     <t>MYTHILI G Y</t>
@@ -4333,7 +4333,7 @@
     <t>Vit52347@123</t>
   </si>
   <si>
-    <t>(multi)52349</t>
+    <t>(MULTI)52349</t>
   </si>
   <si>
     <t>SENTHIL KUMAR A M</t>
@@ -4345,7 +4345,7 @@
     <t>Vit52349@123</t>
   </si>
   <si>
-    <t>(multi)52350</t>
+    <t>(MULTI)52350</t>
   </si>
   <si>
     <t>ASHA JERLIN M</t>
@@ -4357,7 +4357,7 @@
     <t>Vit52350@123</t>
   </si>
   <si>
-    <t>(multi)52353</t>
+    <t>(MULTI)52353</t>
   </si>
   <si>
     <t>YOGESH C</t>
@@ -4369,7 +4369,7 @@
     <t>Vit52353@123</t>
   </si>
   <si>
-    <t>(multi)52361</t>
+    <t>(MULTI)52361</t>
   </si>
   <si>
     <t>T RAJA SREE</t>
@@ -4381,7 +4381,7 @@
     <t>Vit52361@123</t>
   </si>
   <si>
-    <t>(multi)52362</t>
+    <t>(MULTI)52362</t>
   </si>
   <si>
     <t>RUPA MISHRA</t>
@@ -4393,7 +4393,7 @@
     <t>Vit52362@123</t>
   </si>
   <si>
-    <t>(multi)52610</t>
+    <t>(MULTI)52610</t>
   </si>
   <si>
     <t>DOMINIC SAVIO M</t>
@@ -4405,7 +4405,7 @@
     <t>Vit52610@123</t>
   </si>
   <si>
-    <t>(multi)52777</t>
+    <t>(MULTI)52777</t>
   </si>
   <si>
     <t>SENDHIL R</t>
@@ -4417,7 +4417,7 @@
     <t>Vit52777@123</t>
   </si>
   <si>
-    <t>(multi)52792</t>
+    <t>(MULTI)52792</t>
   </si>
   <si>
     <t>VIJAYAPRABAKARAN K</t>
@@ -4429,7 +4429,7 @@
     <t>Vit52792@123</t>
   </si>
   <si>
-    <t>(multi)52798</t>
+    <t>(MULTI)52798</t>
   </si>
   <si>
     <t>SHALINI M G</t>
@@ -4441,7 +4441,7 @@
     <t>Vit52798@123</t>
   </si>
   <si>
-    <t>(multi)52799</t>
+    <t>(MULTI)52799</t>
   </si>
   <si>
     <t>BENIL T</t>
@@ -4453,7 +4453,7 @@
     <t>Vit52799@123</t>
   </si>
   <si>
-    <t>(multi)52803</t>
+    <t>(MULTI)52803</t>
   </si>
   <si>
     <t>SOUMENDU ROY</t>
@@ -4465,7 +4465,7 @@
     <t>Vit52803@123</t>
   </si>
   <si>
-    <t>(multi)52805</t>
+    <t>(MULTI)52805</t>
   </si>
   <si>
     <t>LAKKOJI SATISH</t>
@@ -4477,7 +4477,7 @@
     <t>Vit52805@123</t>
   </si>
   <si>
-    <t>(multi)52811</t>
+    <t>(MULTI)52811</t>
   </si>
   <si>
     <t>KRITI ARYA</t>
@@ -4489,7 +4489,7 @@
     <t>Vit52811@123</t>
   </si>
   <si>
-    <t>(multi)52822</t>
+    <t>(MULTI)52822</t>
   </si>
   <si>
     <t>RAJESH KUMAR MOHAPATRA</t>
@@ -4501,7 +4501,7 @@
     <t>Vit52822@123</t>
   </si>
   <si>
-    <t>(multi)52823</t>
+    <t>(MULTI)52823</t>
   </si>
   <si>
     <t>GANESH N</t>
@@ -4513,7 +4513,7 @@
     <t>Vit52823@123</t>
   </si>
   <si>
-    <t>(multi)52825</t>
+    <t>(MULTI)52825</t>
   </si>
   <si>
     <t>VATCHALA S</t>
@@ -4525,7 +4525,7 @@
     <t>Vit52825@123</t>
   </si>
   <si>
-    <t>(multi)52833</t>
+    <t>(MULTI)52833</t>
   </si>
   <si>
     <t>ILAVENDHAN A</t>
@@ -4537,7 +4537,7 @@
     <t>Vit52833@123</t>
   </si>
   <si>
-    <t>(multi)52836</t>
+    <t>(MULTI)52836</t>
   </si>
   <si>
     <t>VALLIDEVI K</t>
@@ -4549,7 +4549,7 @@
     <t>Vit52836@123</t>
   </si>
   <si>
-    <t>(multi)52846</t>
+    <t>(MULTI)52846</t>
   </si>
   <si>
     <t>SHYAMAPADA NANDI</t>
@@ -4561,7 +4561,7 @@
     <t>Vit52846@123</t>
   </si>
   <si>
-    <t>(multi)52850</t>
+    <t>(MULTI)52850</t>
   </si>
   <si>
     <t>PULAK KONAR</t>
@@ -4573,7 +4573,7 @@
     <t>Vit52850@123</t>
   </si>
   <si>
-    <t>(multi)52851</t>
+    <t>(MULTI)52851</t>
   </si>
   <si>
     <t>S JAHANGEER SIDIQ</t>
@@ -4585,7 +4585,7 @@
     <t>Vit52851@123</t>
   </si>
   <si>
-    <t>(multi)52858</t>
+    <t>(MULTI)52858</t>
   </si>
   <si>
     <t>SUGANYA R</t>
@@ -4597,7 +4597,7 @@
     <t>Vit52858@123</t>
   </si>
   <si>
-    <t>(multi)52859</t>
+    <t>(MULTI)52859</t>
   </si>
   <si>
     <t>SOBITHA AHILA S</t>
@@ -4609,7 +4609,7 @@
     <t>Vit52859@123</t>
   </si>
   <si>
-    <t>(multi)52863</t>
+    <t>(MULTI)52863</t>
   </si>
   <si>
     <t>MANIMARAN J</t>
@@ -4621,7 +4621,7 @@
     <t>Vit52863@123</t>
   </si>
   <si>
-    <t>(multi)52869</t>
+    <t>(MULTI)52869</t>
   </si>
   <si>
     <t>SANDIP DALUI</t>
@@ -4633,7 +4633,7 @@
     <t>Vit52869@123</t>
   </si>
   <si>
-    <t>(multi)52871</t>
+    <t>(MULTI)52871</t>
   </si>
   <si>
     <t>AVINASH KUMAR MITTAL</t>
@@ -4645,7 +4645,7 @@
     <t>Vit52871@123</t>
   </si>
   <si>
-    <t>(multi)52879</t>
+    <t>(MULTI)52879</t>
   </si>
   <si>
     <t>RAJESH R</t>
@@ -4657,7 +4657,7 @@
     <t>Vit52879@123</t>
   </si>
   <si>
-    <t>(multi)52880</t>
+    <t>(MULTI)52880</t>
   </si>
   <si>
     <t>ILAVARASAN T</t>
@@ -4669,7 +4669,7 @@
     <t>Vit52880@123</t>
   </si>
   <si>
-    <t>(multi)52882</t>
+    <t>(MULTI)52882</t>
   </si>
   <si>
     <t>DHANALAKSHMI R</t>
@@ -4681,7 +4681,7 @@
     <t>Vit52882@123</t>
   </si>
   <si>
-    <t>(multi)52883</t>
+    <t>(MULTI)52883</t>
   </si>
   <si>
     <t>PAVITHRA S</t>
@@ -4693,7 +4693,7 @@
     <t>Vit52883@123</t>
   </si>
   <si>
-    <t>(multi)52889</t>
+    <t>(MULTI)52889</t>
   </si>
   <si>
     <t>PRAVIN RENOLD A</t>
@@ -4705,7 +4705,7 @@
     <t>Vit52889@123</t>
   </si>
   <si>
-    <t>(multi)53008</t>
+    <t>(MULTI)53008</t>
   </si>
   <si>
     <t>USHA RANI S</t>
@@ -4717,7 +4717,7 @@
     <t>Vit53008@123</t>
   </si>
   <si>
-    <t>(multi)53009</t>
+    <t>(MULTI)53009</t>
   </si>
   <si>
     <t>MANJU G</t>
@@ -4729,7 +4729,7 @@
     <t>Vit53009@123</t>
   </si>
   <si>
-    <t>(multi)53011</t>
+    <t>(MULTI)53011</t>
   </si>
   <si>
     <t>DEEPIKA ROSELIND J</t>
@@ -4741,7 +4741,7 @@
     <t>Vit53011@123</t>
   </si>
   <si>
-    <t>(multi)53017</t>
+    <t>(MULTI)53017</t>
   </si>
   <si>
     <t>JANNATH NISHA O S</t>
@@ -4753,7 +4753,7 @@
     <t>Vit53017@123</t>
   </si>
   <si>
-    <t>(multi)53019</t>
+    <t>(MULTI)53019</t>
   </si>
   <si>
     <t>V BRINDHA</t>
@@ -4765,7 +4765,7 @@
     <t>Vit53019@123</t>
   </si>
   <si>
-    <t>(multi)53025</t>
+    <t>(MULTI)53025</t>
   </si>
   <si>
     <t>PALANI THANARAJ K</t>
@@ -4777,7 +4777,7 @@
     <t>Vit53025@123</t>
   </si>
   <si>
-    <t>(multi)53027</t>
+    <t>(MULTI)53027</t>
   </si>
   <si>
     <t>SUDHEER KUMAR E</t>
@@ -4789,7 +4789,7 @@
     <t>Vit53027@123</t>
   </si>
   <si>
-    <t>(multi)53028</t>
+    <t>(MULTI)53028</t>
   </si>
   <si>
     <t>MANIGANDAN M</t>
@@ -4801,7 +4801,7 @@
     <t>Vit53028@123</t>
   </si>
   <si>
-    <t>(multi)53029</t>
+    <t>(MULTI)53029</t>
   </si>
   <si>
     <t>KANIMOZHI S</t>
@@ -4813,7 +4813,7 @@
     <t>Vit53029@123</t>
   </si>
   <si>
-    <t>(multi)53030</t>
+    <t>(MULTI)53030</t>
   </si>
   <si>
     <t>DEEPA NIVETHIKA</t>
@@ -4825,7 +4825,7 @@
     <t>Vit53030@123</t>
   </si>
   <si>
-    <t>(multi)53032</t>
+    <t>(MULTI)53032</t>
   </si>
   <si>
     <t>SRIDHAR C</t>
@@ -4837,7 +4837,7 @@
     <t>Vit53032@123</t>
   </si>
   <si>
-    <t>(multi)53034</t>
+    <t>(MULTI)53034</t>
   </si>
   <si>
     <t>ELAKIYA E</t>
@@ -4849,7 +4849,7 @@
     <t>Vit53034@123</t>
   </si>
   <si>
-    <t>(multi)53035</t>
+    <t>(MULTI)53035</t>
   </si>
   <si>
     <t>CHRISTOPHER COLUMBUS C</t>
@@ -4861,7 +4861,7 @@
     <t>Vit53035@123</t>
   </si>
   <si>
-    <t>(multi)53038</t>
+    <t>(MULTI)53038</t>
   </si>
   <si>
     <t>UPENDER P</t>
@@ -4873,7 +4873,7 @@
     <t>Vit53038@123</t>
   </si>
   <si>
-    <t>(multi)53039</t>
+    <t>(MULTI)53039</t>
   </si>
   <si>
     <t>SUVIDHA RUPESH KUMAR</t>
@@ -4885,7 +4885,7 @@
     <t>Vit53039@123</t>
   </si>
   <si>
-    <t>(multi)53041</t>
+    <t>(MULTI)53041</t>
   </si>
   <si>
     <t>MOHIT KUMAR</t>
@@ -4897,7 +4897,7 @@
     <t>Vit53041@123</t>
   </si>
   <si>
-    <t>(multi)53042</t>
+    <t>(MULTI)53042</t>
   </si>
   <si>
     <t>JYOTISMITA MISHRA</t>
@@ -4909,7 +4909,7 @@
     <t>Vit53042@123</t>
   </si>
   <si>
-    <t>(multi)53044</t>
+    <t>(MULTI)53044</t>
   </si>
   <si>
     <t>KRISHNA KUMBA</t>
@@ -4921,7 +4921,7 @@
     <t>Vit53044@123</t>
   </si>
   <si>
-    <t>(multi)53045</t>
+    <t>(MULTI)53045</t>
   </si>
   <si>
     <t>SANDIP KUMAR DAS</t>
@@ -4933,7 +4933,7 @@
     <t>Vit53045@123</t>
   </si>
   <si>
-    <t>(multi)53046</t>
+    <t>(MULTI)53046</t>
   </si>
   <si>
     <t>SRISAKTHI SARAVANAN</t>
@@ -4945,7 +4945,7 @@
     <t>Vit53046@123</t>
   </si>
   <si>
-    <t>(multi)53048</t>
+    <t>(MULTI)53048</t>
   </si>
   <si>
     <t>MALINI DEEPIKA</t>
@@ -4957,7 +4957,7 @@
     <t>Vit53048@123</t>
   </si>
   <si>
-    <t>(multi)53049</t>
+    <t>(MULTI)53049</t>
   </si>
   <si>
     <t>REVATHI A R</t>
@@ -4969,7 +4969,7 @@
     <t>Vit53049@123</t>
   </si>
   <si>
-    <t>(multi)53050</t>
+    <t>(MULTI)53050</t>
   </si>
   <si>
     <t>SANDHYA</t>
@@ -4981,7 +4981,7 @@
     <t>Vit53050@123</t>
   </si>
   <si>
-    <t>(multi)53056</t>
+    <t>(MULTI)53056</t>
   </si>
   <si>
     <t>PRASANNA BHARATHI</t>
@@ -4993,7 +4993,7 @@
     <t>Vit53056@123</t>
   </si>
   <si>
-    <t>(multi)53058</t>
+    <t>(MULTI)53058</t>
   </si>
   <si>
     <t>MITHU SARKAR</t>
@@ -5005,7 +5005,7 @@
     <t>Vit53058@123</t>
   </si>
   <si>
-    <t>(multi)53059</t>
+    <t>(MULTI)53059</t>
   </si>
   <si>
     <t>PRITAM BHATTACHARJEE</t>
@@ -5017,7 +5017,7 @@
     <t>Vit53059@123</t>
   </si>
   <si>
-    <t>(multi)53061</t>
+    <t>(MULTI)53061</t>
   </si>
   <si>
     <t>SUKRITI</t>
@@ -5029,7 +5029,7 @@
     <t>Vit53061@123</t>
   </si>
   <si>
-    <t>(multi)53062</t>
+    <t>(MULTI)53062</t>
   </si>
   <si>
     <t>PARASURAMAN E</t>
@@ -5041,7 +5041,7 @@
     <t>Vit53062@123</t>
   </si>
   <si>
-    <t>(multi)53063</t>
+    <t>(MULTI)53063</t>
   </si>
   <si>
     <t>RATHNA</t>
@@ -5053,7 +5053,7 @@
     <t>Vit53063@123</t>
   </si>
   <si>
-    <t>(multi)53065</t>
+    <t>(MULTI)53065</t>
   </si>
   <si>
     <t>BALAKRISHNAN R</t>
@@ -5065,7 +5065,7 @@
     <t>Vit53065@123</t>
   </si>
   <si>
-    <t>(multi)53066</t>
+    <t>(MULTI)53066</t>
   </si>
   <si>
     <t>RAJU PATEL</t>
@@ -5077,7 +5077,7 @@
     <t>Vit53066@123</t>
   </si>
   <si>
-    <t>(multi)53068</t>
+    <t>(MULTI)53068</t>
   </si>
   <si>
     <t>NAWIN RA</t>
@@ -5089,7 +5089,7 @@
     <t>Vit53068@123</t>
   </si>
   <si>
-    <t>(multi)53069</t>
+    <t>(MULTI)53069</t>
   </si>
   <si>
     <t>AFRUZA BEGUM</t>
@@ -5101,7 +5101,7 @@
     <t>Vit53069@123</t>
   </si>
   <si>
-    <t>(multi)53070</t>
+    <t>(MULTI)53070</t>
   </si>
   <si>
     <t>SRITAMA ROY</t>
@@ -5113,7 +5113,7 @@
     <t>Vit53070@123</t>
   </si>
   <si>
-    <t>(multi)53071</t>
+    <t>(MULTI)53071</t>
   </si>
   <si>
     <t>PRIYANKA DAS</t>
@@ -5125,7 +5125,7 @@
     <t>Vit53071@123</t>
   </si>
   <si>
-    <t>(multi)53072</t>
+    <t>(MULTI)53072</t>
   </si>
   <si>
     <t>SENTHIL KUMAR R</t>
@@ -5137,7 +5137,7 @@
     <t>Vit53072@123</t>
   </si>
   <si>
-    <t>(multi)53073</t>
+    <t>(MULTI)53073</t>
   </si>
   <si>
     <t>SENTHIL PRAKASH P N</t>
@@ -5149,7 +5149,7 @@
     <t>Vit53073@123</t>
   </si>
   <si>
-    <t>(multi)53074</t>
+    <t>(MULTI)53074</t>
   </si>
   <si>
     <t>SUDHARSON S</t>
@@ -5161,7 +5161,7 @@
     <t>Vit53074@123</t>
   </si>
   <si>
-    <t>(multi)53075</t>
+    <t>(MULTI)53075</t>
   </si>
   <si>
     <t>KAJA MOHIDEEN A</t>
@@ -5173,7 +5173,7 @@
     <t>Vit53075@123</t>
   </si>
   <si>
-    <t>(multi)53076</t>
+    <t>(MULTI)53076</t>
   </si>
   <si>
     <t>KARTHIKA V</t>
@@ -5185,7 +5185,7 @@
     <t>Vit53076@123</t>
   </si>
   <si>
-    <t>(multi)53077</t>
+    <t>(MULTI)53077</t>
   </si>
   <si>
     <t>LAKSHMI HARIKA PALIVELA</t>
@@ -5197,7 +5197,7 @@
     <t>Vit53077@123</t>
   </si>
   <si>
-    <t>(multi)53078</t>
+    <t>(MULTI)53078</t>
   </si>
   <si>
     <t>PREMANAND V</t>
@@ -5209,7 +5209,7 @@
     <t>Vit53078@123</t>
   </si>
   <si>
-    <t>(multi)53079</t>
+    <t>(MULTI)53079</t>
   </si>
   <si>
     <t>CHANDRAMAULESHWAR ROY</t>
@@ -5221,7 +5221,7 @@
     <t>Vit53079@123</t>
   </si>
   <si>
-    <t>(multi)53080</t>
+    <t>(MULTI)53080</t>
   </si>
   <si>
     <t>KANNIGA DEVI R</t>
@@ -5233,7 +5233,7 @@
     <t>Vit53080@123</t>
   </si>
   <si>
-    <t>(multi)53087</t>
+    <t>(MULTI)53087</t>
   </si>
   <si>
     <t>SOUMYA RANJAN MAHAPATRO</t>
@@ -5245,7 +5245,7 @@
     <t>Vit53087@123</t>
   </si>
   <si>
-    <t>(multi)53088</t>
+    <t>(MULTI)53088</t>
   </si>
   <si>
     <t>SITHARTHAN R</t>
@@ -5257,7 +5257,7 @@
     <t>Vit53088@123</t>
   </si>
   <si>
-    <t>(multi)53090</t>
+    <t>(MULTI)53090</t>
   </si>
   <si>
     <t>BANUMATHY S</t>
@@ -5269,7 +5269,7 @@
     <t>Vit53090@123</t>
   </si>
   <si>
-    <t>(multi)53091</t>
+    <t>(MULTI)53091</t>
   </si>
   <si>
     <t>RAJAKUMAR R</t>
@@ -5281,7 +5281,7 @@
     <t>Vit53091@123</t>
   </si>
   <si>
-    <t>(multi)53092</t>
+    <t>(MULTI)53092</t>
   </si>
   <si>
     <t>SARAVANA KUMAR R</t>
@@ -5293,7 +5293,7 @@
     <t>Vit53092@123</t>
   </si>
   <si>
-    <t>(multi)53093</t>
+    <t>(MULTI)53093</t>
   </si>
   <si>
     <t>ARAVINDKUMAR S</t>
@@ -5305,7 +5305,7 @@
     <t>Vit53093@123</t>
   </si>
   <si>
-    <t>(multi)53099</t>
+    <t>(MULTI)53099</t>
   </si>
   <si>
     <t>NITISH KATAL</t>
@@ -5317,7 +5317,7 @@
     <t>Vit53099@123</t>
   </si>
   <si>
-    <t>(multi)53101</t>
+    <t>(MULTI)53101</t>
   </si>
   <si>
     <t>AVUTHU AVINASH REDDY</t>
@@ -5329,7 +5329,7 @@
     <t>Vit53101@123</t>
   </si>
   <si>
-    <t>(multi)53103</t>
+    <t>(MULTI)53103</t>
   </si>
   <si>
     <t>PADMANABAN R</t>
@@ -5341,7 +5341,7 @@
     <t>Vit53103@123</t>
   </si>
   <si>
-    <t>(multi)53104</t>
+    <t>(MULTI)53104</t>
   </si>
   <si>
     <t>RAJA M</t>
@@ -5353,7 +5353,7 @@
     <t>Vit53104@123</t>
   </si>
   <si>
-    <t>(multi)53105</t>
+    <t>(MULTI)53105</t>
   </si>
   <si>
     <t>BALASARASWATHI</t>
@@ -5365,7 +5365,7 @@
     <t>Vit53105@123</t>
   </si>
   <si>
-    <t>(multi)53112</t>
+    <t>(MULTI)53112</t>
   </si>
   <si>
     <t>KARTHIKEYAN N</t>
@@ -5377,7 +5377,7 @@
     <t>Vit53112@123</t>
   </si>
   <si>
-    <t>(multi)53122</t>
+    <t>(MULTI)53122</t>
   </si>
   <si>
     <t>DHANUSH R</t>
@@ -5389,7 +5389,7 @@
     <t>Vit53122@123</t>
   </si>
   <si>
-    <t>(multi)53123</t>
+    <t>(MULTI)53123</t>
   </si>
   <si>
     <t>SANKARSAN TARAI</t>
@@ -5401,7 +5401,7 @@
     <t>Vit53123@123</t>
   </si>
   <si>
-    <t>(multi)53124</t>
+    <t>(MULTI)53124</t>
   </si>
   <si>
     <t>SUBITHA D</t>
@@ -5413,7 +5413,7 @@
     <t>Vit53124@123</t>
   </si>
   <si>
-    <t>(multi)53126</t>
+    <t>(MULTI)53126</t>
   </si>
   <si>
     <t>KABILAN K</t>
@@ -5425,7 +5425,7 @@
     <t>Vit53126@123</t>
   </si>
   <si>
-    <t>(multi)53127</t>
+    <t>(MULTI)53127</t>
   </si>
   <si>
     <t>KAVITHA J C</t>
@@ -5437,7 +5437,7 @@
     <t>Vit53127@123</t>
   </si>
   <si>
-    <t>(multi)53128</t>
+    <t>(MULTI)53128</t>
   </si>
   <si>
     <t>SIVAKAMI R</t>
@@ -5449,7 +5449,7 @@
     <t>Vit53128@123</t>
   </si>
   <si>
-    <t>(multi)53129</t>
+    <t>(MULTI)53129</t>
   </si>
   <si>
     <t>PADMAJA N</t>
@@ -5461,7 +5461,7 @@
     <t>Vit53129@123</t>
   </si>
   <si>
-    <t>(multi)53131</t>
+    <t>(MULTI)53131</t>
   </si>
   <si>
     <t>ANIK GOSWAMI</t>
@@ -5473,7 +5473,7 @@
     <t>Vit53131@123</t>
   </si>
   <si>
-    <t>(multi)53134</t>
+    <t>(MULTI)53134</t>
   </si>
   <si>
     <t>VALARMATHI K</t>
@@ -5485,7 +5485,7 @@
     <t>Vit53134@123</t>
   </si>
   <si>
-    <t>(multi)53136</t>
+    <t>(MULTI)53136</t>
   </si>
   <si>
     <t>SRIDEVI S</t>
@@ -5497,7 +5497,7 @@
     <t>Vit53136@123</t>
   </si>
   <si>
-    <t>(multi)53137</t>
+    <t>(MULTI)53137</t>
   </si>
   <si>
     <t>DHAVAKUMAR P</t>
@@ -5509,7 +5509,7 @@
     <t>Vit53137@123</t>
   </si>
   <si>
-    <t>(multi)53139</t>
+    <t>(MULTI)53139</t>
   </si>
   <si>
     <t>INDIRA B</t>
@@ -5521,7 +5521,7 @@
     <t>Vit53139@123</t>
   </si>
   <si>
-    <t>(multi)53140</t>
+    <t>(MULTI)53140</t>
   </si>
   <si>
     <t>JEAN JENIFER NESAM J</t>
@@ -5533,7 +5533,7 @@
     <t>Vit53140@123</t>
   </si>
   <si>
-    <t>(multi)53145</t>
+    <t>(MULTI)53145</t>
   </si>
   <si>
     <t>VIGNESH U</t>
@@ -5545,7 +5545,7 @@
     <t>Vit53145@123</t>
   </si>
   <si>
-    <t>(multi)53153</t>
+    <t>(MULTI)53153</t>
   </si>
   <si>
     <t>KISHOR KISAN INGLE</t>
@@ -5557,7 +5557,7 @@
     <t>Vit53153@123</t>
   </si>
   <si>
-    <t>(multi)53154</t>
+    <t>(MULTI)53154</t>
   </si>
   <si>
     <t>RAMA PARVATHY L</t>
@@ -5569,7 +5569,7 @@
     <t>Vit53154@123</t>
   </si>
   <si>
-    <t>(multi)53155</t>
+    <t>(MULTI)53155</t>
   </si>
   <si>
     <t>KARTHIKEYAN P R</t>
@@ -5581,7 +5581,7 @@
     <t>Vit53155@123</t>
   </si>
   <si>
-    <t>(multi)53157</t>
+    <t>(MULTI)53157</t>
   </si>
   <si>
     <t>SARAVANAN P</t>
@@ -5593,7 +5593,7 @@
     <t>Vit53157@123</t>
   </si>
   <si>
-    <t>(multi)53159</t>
+    <t>(MULTI)53159</t>
   </si>
   <si>
     <t>RENUKA DEVI R</t>
@@ -5605,7 +5605,7 @@
     <t>Vit53159@123</t>
   </si>
   <si>
-    <t>(multi)53160</t>
+    <t>(MULTI)53160</t>
   </si>
   <si>
     <t>POONKODI</t>
@@ -5617,7 +5617,7 @@
     <t>Vit53160@123</t>
   </si>
   <si>
-    <t>(multi)53161</t>
+    <t>(MULTI)53161</t>
   </si>
   <si>
     <t>PREM SANKAR</t>
@@ -5629,7 +5629,7 @@
     <t>Vit53161@123</t>
   </si>
   <si>
-    <t>(multi)53164</t>
+    <t>(MULTI)53164</t>
   </si>
   <si>
     <t>AHADIT</t>
@@ -5641,7 +5641,7 @@
     <t>Vit53164@123</t>
   </si>
   <si>
-    <t>(multi)53166</t>
+    <t>(MULTI)53166</t>
   </si>
   <si>
     <t>MARIMUTHU</t>
@@ -5653,7 +5653,7 @@
     <t>Vit53166@123</t>
   </si>
   <si>
-    <t>(multi)53343</t>
+    <t>(MULTI)53343</t>
   </si>
   <si>
     <t>LEKSHMI K</t>
@@ -5665,7 +5665,7 @@
     <t>Vit53343@123</t>
   </si>
   <si>
-    <t>(multi)53368</t>
+    <t>(MULTI)53368</t>
   </si>
   <si>
     <t>LOGESWARI G</t>
@@ -5677,7 +5677,7 @@
     <t>Vit53368@123</t>
   </si>
   <si>
-    <t>(multi)53376</t>
+    <t>(MULTI)53376</t>
   </si>
   <si>
     <t>NIVETHITHA V</t>
@@ -5689,7 +5689,7 @@
     <t>Vit53376@123</t>
   </si>
   <si>
-    <t>(multi)53379</t>
+    <t>(MULTI)53379</t>
   </si>
   <si>
     <t>SUBHAYAN DEY</t>
@@ -5701,7 +5701,7 @@
     <t>Vit53379@123</t>
   </si>
   <si>
-    <t>(multi)53382</t>
+    <t>(MULTI)53382</t>
   </si>
   <si>
     <t>SREEJA P S</t>
@@ -5713,7 +5713,7 @@
     <t>Vit53382@123</t>
   </si>
   <si>
-    <t>(multi)53383</t>
+    <t>(MULTI)53383</t>
   </si>
   <si>
     <t>ANISHA NATARAJAN</t>
@@ -5725,7 +5725,7 @@
     <t>Vit53383@123</t>
   </si>
   <si>
-    <t>(multi)53386</t>
+    <t>(MULTI)53386</t>
   </si>
   <si>
     <t>ARAVIND C K</t>
@@ -5737,7 +5737,7 @@
     <t>Vit53386@123</t>
   </si>
   <si>
-    <t>(multi)53388</t>
+    <t>(MULTI)53388</t>
   </si>
   <si>
     <t>KAVIPRIYA G</t>
@@ -5749,7 +5749,7 @@
     <t>Vit53388@123</t>
   </si>
   <si>
-    <t>(multi)53391</t>
+    <t>(MULTI)53391</t>
   </si>
   <si>
     <t>SELVAM D</t>
@@ -5761,7 +5761,7 @@
     <t>Vit53391@123</t>
   </si>
   <si>
-    <t>(multi)53393</t>
+    <t>(MULTI)53393</t>
   </si>
   <si>
     <t>NATARAJAN B</t>
@@ -5773,7 +5773,7 @@
     <t>Vit53393@123</t>
   </si>
   <si>
-    <t>(multi)53394</t>
+    <t>(MULTI)53394</t>
   </si>
   <si>
     <t>TANMOY MAJUMDER</t>
@@ -5785,7 +5785,7 @@
     <t>Vit53394@123</t>
   </si>
   <si>
-    <t>(multi)53398</t>
+    <t>(MULTI)53398</t>
   </si>
   <si>
     <t>SANTHI V</t>
@@ -5797,7 +5797,7 @@
     <t>Vit53398@123</t>
   </si>
   <si>
-    <t>(multi)53401</t>
+    <t>(MULTI)53401</t>
   </si>
   <si>
     <t>N RAMESH BABU</t>
@@ -5809,7 +5809,7 @@
     <t>Vit53401@123</t>
   </si>
   <si>
-    <t>(multi)53408</t>
+    <t>(MULTI)53408</t>
   </si>
   <si>
     <t>PADMA J</t>
@@ -5821,7 +5821,7 @@
     <t>Vit53408@123</t>
   </si>
   <si>
-    <t>(multi)53546</t>
+    <t>(MULTI)53546</t>
   </si>
   <si>
     <t>THANIKACHALAM V</t>
@@ -5833,7 +5833,7 @@
     <t>Vit53546@123</t>
   </si>
   <si>
-    <t>(multi)53552</t>
+    <t>(MULTI)53552</t>
   </si>
   <si>
     <t>ROLLA SUBRAHMANYAM</t>
@@ -5845,7 +5845,7 @@
     <t>Vit53552@123</t>
   </si>
   <si>
-    <t>(multi)53558</t>
+    <t>(MULTI)53558</t>
   </si>
   <si>
     <t>PRABHA B</t>
@@ -5857,7 +5857,7 @@
     <t>Vit53558@123</t>
   </si>
   <si>
-    <t>(multi)53566</t>
+    <t>(MULTI)53566</t>
   </si>
   <si>
     <t>SELLAM V</t>
@@ -5869,7 +5869,7 @@
     <t>Vit53566@123</t>
   </si>
   <si>
-    <t>(multi)53567</t>
+    <t>(MULTI)53567</t>
   </si>
   <si>
     <t>SHREE PRAKASH</t>
@@ -5881,7 +5881,7 @@
     <t>Vit53567@123</t>
   </si>
   <si>
-    <t>(multi)53568</t>
+    <t>(MULTI)53568</t>
   </si>
   <si>
     <t>SOFTYA SEBASTIAN</t>
@@ -5893,7 +5893,7 @@
     <t>Vit53568@123</t>
   </si>
   <si>
-    <t>(multi)53598</t>
+    <t>(MULTI)53598</t>
   </si>
   <si>
     <t>TAHIR MUJTABA</t>
@@ -5905,7 +5905,7 @@
     <t>Vit53598@123</t>
   </si>
   <si>
-    <t>(multi)53603</t>
+    <t>(MULTI)53603</t>
   </si>
   <si>
     <t>SAHELI KARMAKAR</t>
@@ -5917,7 +5917,7 @@
     <t>Vit53603@123</t>
   </si>
   <si>
-    <t>(multi)53608</t>
+    <t>(MULTI)53608</t>
   </si>
   <si>
     <t>BENILA S</t>
@@ -5929,7 +5929,7 @@
     <t>Vit53608@123</t>
   </si>
   <si>
-    <t>(multi)53609</t>
+    <t>(MULTI)53609</t>
   </si>
   <si>
     <t>SIVARAMAKRISHNAN N</t>
@@ -5941,7 +5941,7 @@
     <t>Vit53609@123</t>
   </si>
   <si>
-    <t>(multi)53610</t>
+    <t>(MULTI)53610</t>
   </si>
   <si>
     <t>KUMARAN K</t>
@@ -5953,7 +5953,7 @@
     <t>Vit53610@123</t>
   </si>
   <si>
-    <t>(multi)53612</t>
+    <t>(MULTI)53612</t>
   </si>
   <si>
     <t>RAJESH KUMAR K</t>
@@ -5965,7 +5965,7 @@
     <t>Vit53612@123</t>
   </si>
   <si>
-    <t>(multi)53613</t>
+    <t>(MULTI)53613</t>
   </si>
   <si>
     <t>MOGANA PRIYA C</t>
@@ -5977,7 +5977,7 @@
     <t>Vit53613@123</t>
   </si>
   <si>
-    <t>(multi)53615</t>
+    <t>(MULTI)53615</t>
   </si>
   <si>
     <t>BALRAJ E</t>
@@ -5989,7 +5989,7 @@
     <t>Vit53615@123</t>
   </si>
   <si>
-    <t>(multi)53616</t>
+    <t>(MULTI)53616</t>
   </si>
   <si>
     <t>HELEN VIJITHA P</t>
@@ -6001,7 +6001,7 @@
     <t>Vit53616@123</t>
   </si>
   <si>
-    <t>(multi)53617</t>
+    <t>(MULTI)53617</t>
   </si>
   <si>
     <t>DEVI K</t>
@@ -6013,7 +6013,7 @@
     <t>Vit53617@123</t>
   </si>
   <si>
-    <t>(multi)53618</t>
+    <t>(MULTI)53618</t>
   </si>
   <si>
     <t>SAKTHIVEL R</t>
@@ -6025,7 +6025,7 @@
     <t>Vit53618@123</t>
   </si>
   <si>
-    <t>(multi)53619</t>
+    <t>(MULTI)53619</t>
   </si>
   <si>
     <t>(multi)manikandan.pr@vit.ac.in</t>
@@ -6034,7 +6034,7 @@
     <t>Vit53619@123</t>
   </si>
   <si>
-    <t>(multi)53620</t>
+    <t>(MULTI)53620</t>
   </si>
   <si>
     <t>KIRAN KUMAR M</t>
@@ -6046,7 +6046,7 @@
     <t>Vit53620@123</t>
   </si>
   <si>
-    <t>(multi)53622</t>
+    <t>(MULTI)53622</t>
   </si>
   <si>
     <t>MANMOHAN SHARMA</t>
@@ -6058,7 +6058,7 @@
     <t>Vit53622@123</t>
   </si>
   <si>
-    <t>(multi)53623</t>
+    <t>(MULTI)53623</t>
   </si>
   <si>
     <t>SARANYARAJ D</t>
@@ -6070,7 +6070,7 @@
     <t>Vit53623@123</t>
   </si>
   <si>
-    <t>(multi)53624</t>
+    <t>(MULTI)53624</t>
   </si>
   <si>
     <t>HEMALATHA K</t>
@@ -6082,7 +6082,7 @@
     <t>Vit53624@123</t>
   </si>
   <si>
-    <t>(multi)53626</t>
+    <t>(MULTI)53626</t>
   </si>
   <si>
     <t>JAI VINITA L</t>
@@ -6094,7 +6094,7 @@
     <t>Vit53626@123</t>
   </si>
   <si>
-    <t>(multi)53627</t>
+    <t>(MULTI)53627</t>
   </si>
   <si>
     <t>PARVATHY A K</t>
@@ -6106,7 +6106,7 @@
     <t>Vit53627@123</t>
   </si>
   <si>
-    <t>(multi)53629</t>
+    <t>(MULTI)53629</t>
   </si>
   <si>
     <t>JEIPRATHA P N</t>
@@ -6118,7 +6118,7 @@
     <t>Vit53629@123</t>
   </si>
   <si>
-    <t>(multi)53630</t>
+    <t>(MULTI)53630</t>
   </si>
   <si>
     <t>SAMBATH M</t>
@@ -6130,7 +6130,7 @@
     <t>Vit53630@123</t>
   </si>
   <si>
-    <t>(multi)53631</t>
+    <t>(MULTI)53631</t>
   </si>
   <si>
     <t>RATHINAMOORTHY R</t>
@@ -6142,7 +6142,7 @@
     <t>Vit53631@123</t>
   </si>
   <si>
-    <t>(multi)53633</t>
+    <t>(MULTI)53633</t>
   </si>
   <si>
     <t>RANJITH KUMAR M</t>
@@ -6154,7 +6154,7 @@
     <t>Vit53633@123</t>
   </si>
   <si>
-    <t>(multi)53634</t>
+    <t>(MULTI)53634</t>
   </si>
   <si>
     <t>AVADHESH KUMAR SHARMA</t>
@@ -6166,7 +6166,7 @@
     <t>Vit53634@123</t>
   </si>
   <si>
-    <t>(multi)53635</t>
+    <t>(MULTI)53635</t>
   </si>
   <si>
     <t>BALAJI B</t>
@@ -6178,7 +6178,7 @@
     <t>Vit53635@123</t>
   </si>
   <si>
-    <t>(multi)53637</t>
+    <t>(MULTI)53637</t>
   </si>
   <si>
     <t>SARANYA G</t>
@@ -6190,7 +6190,7 @@
     <t>Vit53637@123</t>
   </si>
   <si>
-    <t>(multi)53638</t>
+    <t>(MULTI)53638</t>
   </si>
   <si>
     <t>OMANA J</t>
@@ -6202,7 +6202,7 @@
     <t>Vit53638@123</t>
   </si>
   <si>
-    <t>(multi)53640</t>
+    <t>(MULTI)53640</t>
   </si>
   <si>
     <t>SHENBAGA VELU P</t>
@@ -6214,7 +6214,7 @@
     <t>Vit53640@123</t>
   </si>
   <si>
-    <t>(multi)53641</t>
+    <t>(MULTI)53641</t>
   </si>
   <si>
     <t>VIDHYA LAKSHMI M</t>
@@ -6226,7 +6226,7 @@
     <t>Vit53641@123</t>
   </si>
   <si>
-    <t>(multi)53644</t>
+    <t>(MULTI)53644</t>
   </si>
   <si>
     <t>KRISHANU GANGULY</t>
@@ -6238,7 +6238,7 @@
     <t>Vit53644@123</t>
   </si>
   <si>
-    <t>(multi)53645</t>
+    <t>(MULTI)53645</t>
   </si>
   <si>
     <t>SIVA PRIYA M S</t>
@@ -6250,7 +6250,7 @@
     <t>Vit53645@123</t>
   </si>
   <si>
-    <t>(multi)53646</t>
+    <t>(MULTI)53646</t>
   </si>
   <si>
     <t>VIVEKANANDAN M</t>
@@ -6262,7 +6262,7 @@
     <t>Vit53646@123</t>
   </si>
   <si>
-    <t>(multi)53647</t>
+    <t>(MULTI)53647</t>
   </si>
   <si>
     <t>KSHMA TRIVEDI</t>
@@ -6274,7 +6274,7 @@
     <t>Vit53647@123</t>
   </si>
   <si>
-    <t>(multi)53648</t>
+    <t>(MULTI)53648</t>
   </si>
   <si>
     <t>BHUPESH SINGH KATIYAR</t>
@@ -6286,7 +6286,7 @@
     <t>Vit53648@123</t>
   </si>
   <si>
-    <t>(multi)53650</t>
+    <t>(MULTI)53650</t>
   </si>
   <si>
     <t>PRABHAKAR KUSHWAHA</t>
@@ -6298,7 +6298,7 @@
     <t>Vit53650@123</t>
   </si>
   <si>
-    <t>(multi)53654</t>
+    <t>(MULTI)53654</t>
   </si>
   <si>
     <t>ANSHUMAN DAS</t>
@@ -6310,7 +6310,7 @@
     <t>Vit53654@123</t>
   </si>
   <si>
-    <t>(multi)53655</t>
+    <t>(MULTI)53655</t>
   </si>
   <si>
     <t>LINDA JOSEPH</t>
@@ -6322,7 +6322,7 @@
     <t>Vit53655@123</t>
   </si>
   <si>
-    <t>(multi)53658</t>
+    <t>(MULTI)53658</t>
   </si>
   <si>
     <t>JITENDRA NARAYAN DASH</t>
@@ -6334,7 +6334,7 @@
     <t>Vit53658@123</t>
   </si>
   <si>
-    <t>(multi)53661</t>
+    <t>(MULTI)53661</t>
   </si>
   <si>
     <t>JOHANAN JOYSINGH S</t>
@@ -6346,7 +6346,7 @@
     <t>Vit53661@123</t>
   </si>
   <si>
-    <t>(multi)53669</t>
+    <t>(MULTI)53669</t>
   </si>
   <si>
     <t>LATHA P</t>
@@ -6358,7 +6358,7 @@
     <t>Vit53669@123</t>
   </si>
   <si>
-    <t>(multi)53672</t>
+    <t>(MULTI)53672</t>
   </si>
   <si>
     <t>SUMAN SAHA</t>
@@ -6370,7 +6370,7 @@
     <t>Vit53672@123</t>
   </si>
   <si>
-    <t>(multi)53673</t>
+    <t>(MULTI)53673</t>
   </si>
   <si>
     <t>SWETHA R KUMAR</t>
@@ -6382,7 +6382,7 @@
     <t>Vit53673@123</t>
   </si>
   <si>
-    <t>(multi)53674</t>
+    <t>(MULTI)53674</t>
   </si>
   <si>
     <t>K UMA MAHESWARI</t>
@@ -6394,7 +6394,7 @@
     <t>Vit53674@123</t>
   </si>
   <si>
-    <t>(multi)53683</t>
+    <t>(MULTI)53683</t>
   </si>
   <si>
     <t>SUHASINI S</t>
@@ -6406,7 +6406,7 @@
     <t>Vit53683@123</t>
   </si>
   <si>
-    <t>(multi)53684</t>
+    <t>(MULTI)53684</t>
   </si>
   <si>
     <t>MOHAMMED AARIF K O</t>
@@ -6418,7 +6418,7 @@
     <t>Vit53684@123</t>
   </si>
   <si>
-    <t>(multi)53685</t>
+    <t>(MULTI)53685</t>
   </si>
   <si>
     <t>SUDHA C</t>
@@ -6430,7 +6430,7 @@
     <t>Vit53685@123</t>
   </si>
   <si>
-    <t>(multi)53686</t>
+    <t>(MULTI)53686</t>
   </si>
   <si>
     <t>KULDEEP YADAV</t>
@@ -6442,7 +6442,7 @@
     <t>Vit53686@123</t>
   </si>
   <si>
-    <t>(multi)53689</t>
+    <t>(MULTI)53689</t>
   </si>
   <si>
     <t>JOSHUA SUNDER DAVID REDDIPOGU</t>
@@ -6454,7 +6454,7 @@
     <t>Vit53689@123</t>
   </si>
   <si>
-    <t>(multi)53694</t>
+    <t>(MULTI)53694</t>
   </si>
   <si>
     <t>PRETHIJA G</t>
@@ -6466,7 +6466,7 @@
     <t>Vit53694@123</t>
   </si>
   <si>
-    <t>(multi)53695</t>
+    <t>(MULTI)53695</t>
   </si>
   <si>
     <t>GAYATHRI DEVI S</t>
@@ -6478,7 +6478,7 @@
     <t>Vit53695@123</t>
   </si>
   <si>
-    <t>(multi)53696</t>
+    <t>(MULTI)53696</t>
   </si>
   <si>
     <t>MADURA MEENAKSHI R</t>
@@ -6490,7 +6490,7 @@
     <t>Vit53696@123</t>
   </si>
   <si>
-    <t>(multi)53877</t>
+    <t>(MULTI)53877</t>
   </si>
   <si>
     <t>UMESH K</t>
@@ -6502,7 +6502,7 @@
     <t>Vit53877@123</t>
   </si>
   <si>
-    <t>(multi)53888</t>
+    <t>(MULTI)53888</t>
   </si>
   <si>
     <t>KARTHIKA S K</t>
@@ -6514,7 +6514,7 @@
     <t>Vit53888@123</t>
   </si>
   <si>
-    <t>(multi)53889</t>
+    <t>(MULTI)53889</t>
   </si>
   <si>
     <t>MALINI A</t>
@@ -6526,7 +6526,7 @@
     <t>Vit53889@123</t>
   </si>
   <si>
-    <t>(multi)53900</t>
+    <t>(MULTI)53900</t>
   </si>
   <si>
     <t>SIVARANJANI N</t>
@@ -6538,7 +6538,7 @@
     <t>Vit53900@123</t>
   </si>
   <si>
-    <t>(multi)53913</t>
+    <t>(MULTI)53913</t>
   </si>
   <si>
     <t>IMMANUEL SELWYN RAJ A</t>
@@ -6550,7 +6550,7 @@
     <t>Vit53913@123</t>
   </si>
   <si>
-    <t>(multi)53914</t>
+    <t>(MULTI)53914</t>
   </si>
   <si>
     <t>JOHN RAJAN A</t>
@@ -6562,7 +6562,7 @@
     <t>Vit53914@123</t>
   </si>
   <si>
-    <t>(multi)53915</t>
+    <t>(MULTI)53915</t>
   </si>
   <si>
     <t>VENKADAVARAHAN</t>
@@ -6574,7 +6574,7 @@
     <t>Vit53915@123</t>
   </si>
   <si>
-    <t>(multi)54128</t>
+    <t>(MULTI)54128</t>
   </si>
   <si>
     <t>E INIYA NEHRU</t>
@@ -6586,7 +6586,7 @@
     <t>Vit54128@123</t>
   </si>
   <si>
-    <t>(multi)54142</t>
+    <t>(MULTI)54142</t>
   </si>
   <si>
     <t>PRADEEP N</t>
@@ -6598,7 +6598,7 @@
     <t>Vit54142@123</t>
   </si>
   <si>
-    <t>(multi)54143</t>
+    <t>(MULTI)54143</t>
   </si>
   <si>
     <t>RAJESH GOSWAMI</t>
@@ -6610,7 +6610,7 @@
     <t>Vit54143@123</t>
   </si>
   <si>
-    <t>(multi)54144</t>
+    <t>(MULTI)54144</t>
   </si>
   <si>
     <t>BONDA ATCHUTA GANESH YUVA RAJU</t>
@@ -6622,7 +6622,7 @@
     <t>Vit54144@123</t>
   </si>
   <si>
-    <t>(multi)54145</t>
+    <t>(MULTI)54145</t>
   </si>
   <si>
     <t>ARULMANI S</t>
@@ -6634,7 +6634,7 @@
     <t>Vit54145@123</t>
   </si>
   <si>
-    <t>(multi)54146</t>
+    <t>(MULTI)54146</t>
   </si>
   <si>
     <t>POORNIMA S</t>
@@ -6646,7 +6646,7 @@
     <t>Vit54146@123</t>
   </si>
   <si>
-    <t>(multi)54147</t>
+    <t>(MULTI)54147</t>
   </si>
   <si>
     <t>S VIGNESHWARI</t>
@@ -6658,7 +6658,7 @@
     <t>Vit54147@123</t>
   </si>
   <si>
-    <t>(multi)54148</t>
+    <t>(MULTI)54148</t>
   </si>
   <si>
     <t>VINU MOHAN A M</t>
@@ -6670,7 +6670,7 @@
     <t>Vit54148@123</t>
   </si>
   <si>
-    <t>(multi)54149</t>
+    <t>(MULTI)54149</t>
   </si>
   <si>
     <t>SUJATHA M</t>
@@ -6682,7 +6682,7 @@
     <t>Vit54149@123</t>
   </si>
   <si>
-    <t>(multi)54151</t>
+    <t>(MULTI)54151</t>
   </si>
   <si>
     <t>AARTHI B</t>
@@ -6694,7 +6694,7 @@
     <t>Vit54151@123</t>
   </si>
   <si>
-    <t>(multi)54152</t>
+    <t>(MULTI)54152</t>
   </si>
   <si>
     <t>AMIT KUMAR</t>
@@ -6706,7 +6706,7 @@
     <t>Vit54152@123</t>
   </si>
   <si>
-    <t>(multi)54156</t>
+    <t>(MULTI)54156</t>
   </si>
   <si>
     <t>RANJANI SESHADRI</t>
@@ -6718,7 +6718,7 @@
     <t>Vit54156@123</t>
   </si>
   <si>
-    <t>(multi)54158</t>
+    <t>(MULTI)54158</t>
   </si>
   <si>
     <t>DAYASINDHU DEY</t>
@@ -6730,7 +6730,7 @@
     <t>Vit54158@123</t>
   </si>
   <si>
-    <t>(multi)54159</t>
+    <t>(MULTI)54159</t>
   </si>
   <si>
     <t>ESWARAN M</t>
@@ -6742,7 +6742,7 @@
     <t>Vit54159@123</t>
   </si>
   <si>
-    <t>(multi)54160</t>
+    <t>(MULTI)54160</t>
   </si>
   <si>
     <t>KOWSIGAN M</t>
@@ -6754,7 +6754,7 @@
     <t>Vit54160@123</t>
   </si>
   <si>
-    <t>(multi)54162</t>
+    <t>(MULTI)54162</t>
   </si>
   <si>
     <t>SRIRAMAN R</t>
@@ -6766,7 +6766,7 @@
     <t>Vit54162@123</t>
   </si>
   <si>
-    <t>(multi)54164</t>
+    <t>(MULTI)54164</t>
   </si>
   <si>
     <t>MD SADULLAH</t>
@@ -6778,7 +6778,7 @@
     <t>Vit54164@123</t>
   </si>
   <si>
-    <t>(multi)54165</t>
+    <t>(MULTI)54165</t>
   </si>
   <si>
     <t>PRASAD JONES CHRISTYDASS S</t>
@@ -6790,7 +6790,7 @@
     <t>Vit54165@123</t>
   </si>
   <si>
-    <t>(multi)54167</t>
+    <t>(MULTI)54167</t>
   </si>
   <si>
     <t>ABHIJIT MISHRA</t>
@@ -6802,7 +6802,7 @@
     <t>Vit54167@123</t>
   </si>
   <si>
-    <t>(multi)54168</t>
+    <t>(MULTI)54168</t>
   </si>
   <si>
     <t>AKASH KUMAR PRADHAN</t>
@@ -6814,7 +6814,7 @@
     <t>Vit54168@123</t>
   </si>
   <si>
-    <t>(multi)54169</t>
+    <t>(MULTI)54169</t>
   </si>
   <si>
     <t>BASUA DEBANANDA</t>
@@ -6826,7 +6826,7 @@
     <t>Vit54169@123</t>
   </si>
   <si>
-    <t>(multi)54170</t>
+    <t>(MULTI)54170</t>
   </si>
   <si>
     <t>MOHD IMRAN IDRISI</t>
@@ -6838,7 +6838,7 @@
     <t>Vit54170@123</t>
   </si>
   <si>
-    <t>(multi)54171</t>
+    <t>(MULTI)54171</t>
   </si>
   <si>
     <t>GANESH M</t>
@@ -6850,7 +6850,7 @@
     <t>Vit54171@123</t>
   </si>
   <si>
-    <t>(multi)54173</t>
+    <t>(MULTI)54173</t>
   </si>
   <si>
     <t>ELAKYA R</t>
@@ -6862,7 +6862,7 @@
     <t>Vit54173@123</t>
   </si>
   <si>
-    <t>(multi)54175</t>
+    <t>(MULTI)54175</t>
   </si>
   <si>
     <t>KARTHIKA PICHAIMUTHU</t>
@@ -6874,7 +6874,7 @@
     <t>Vit54175@123</t>
   </si>
   <si>
-    <t>(multi)54177</t>
+    <t>(MULTI)54177</t>
   </si>
   <si>
     <t>SAURABH KUMAR SRIVASTAVA</t>
@@ -6886,7 +6886,7 @@
     <t>Vit54177@123</t>
   </si>
   <si>
-    <t>(multi)54178</t>
+    <t>(MULTI)54178</t>
   </si>
   <si>
     <t>SHAIK AHMADSAIDULU</t>
@@ -6898,7 +6898,7 @@
     <t>Vit54178@123</t>
   </si>
   <si>
-    <t>(multi)54179</t>
+    <t>(MULTI)54179</t>
   </si>
   <si>
     <t>BIBHUTI BHUSAN PRADHAN</t>
@@ -6910,7 +6910,7 @@
     <t>Vit54179@123</t>
   </si>
   <si>
-    <t>(multi)54181</t>
+    <t>(MULTI)54181</t>
   </si>
   <si>
     <t>PRAVEEN JARAUT</t>
@@ -6922,7 +6922,7 @@
     <t>Vit54181@123</t>
   </si>
   <si>
-    <t>(multi)54183</t>
+    <t>(MULTI)54183</t>
   </si>
   <si>
     <t>SANKARI M</t>
@@ -6934,7 +6934,7 @@
     <t>Vit54183@123</t>
   </si>
   <si>
-    <t>(multi)54189</t>
+    <t>(MULTI)54189</t>
   </si>
   <si>
     <t>NAZEER ANSARI</t>
@@ -6946,7 +6946,7 @@
     <t>Vit54189@123</t>
   </si>
   <si>
-    <t>(multi)54190</t>
+    <t>(MULTI)54190</t>
   </si>
   <si>
     <t>PONNUSAMY P</t>
@@ -6958,7 +6958,7 @@
     <t>Vit54190@123</t>
   </si>
   <si>
-    <t>(multi)54191</t>
+    <t>(MULTI)54191</t>
   </si>
   <si>
     <t>VIJAYAPRIYA R</t>
@@ -6970,7 +6970,7 @@
     <t>Vit54191@123</t>
   </si>
   <si>
-    <t>(multi)54192</t>
+    <t>(MULTI)54192</t>
   </si>
   <si>
     <t>SUNIT KUMAR</t>
@@ -6982,7 +6982,7 @@
     <t>Vit54192@123</t>
   </si>
   <si>
-    <t>(multi)54193</t>
+    <t>(MULTI)54193</t>
   </si>
   <si>
     <t>SEBINA YESMIN</t>
@@ -6994,7 +6994,7 @@
     <t>Vit54193@123</t>
   </si>
   <si>
-    <t>(multi)54424</t>
+    <t>(MULTI)54424</t>
   </si>
   <si>
     <t>KARTHIK S</t>
@@ -7006,7 +7006,7 @@
     <t>Vit54424@123</t>
   </si>
   <si>
-    <t>(multi)54425</t>
+    <t>(MULTI)54425</t>
   </si>
   <si>
     <t>THANGARAJ M</t>
@@ -7018,7 +7018,7 @@
     <t>Vit54425@123</t>
   </si>
   <si>
-    <t>(multi)54508</t>
+    <t>(MULTI)54508</t>
   </si>
   <si>
     <t>SUHAIL K</t>
@@ -7030,7 +7030,7 @@
     <t>Vit54508@123</t>
   </si>
   <si>
-    <t>(multi)54510</t>
+    <t>(MULTI)54510</t>
   </si>
   <si>
     <t>SINDHU RAVINDRAN</t>
@@ -7042,7 +7042,7 @@
     <t>Vit54510@123</t>
   </si>
   <si>
-    <t>(multi)54517</t>
+    <t>(MULTI)54517</t>
   </si>
   <si>
     <t>SRINIVASAN B</t>
@@ -7054,7 +7054,7 @@
     <t>Vit54517@123</t>
   </si>
   <si>
-    <t>(multi)54527</t>
+    <t>(MULTI)54527</t>
   </si>
   <si>
     <t>RAJKUMAR R</t>
@@ -7066,7 +7066,7 @@
     <t>Vit54527@123</t>
   </si>
   <si>
-    <t>(multi)54652</t>
+    <t>(MULTI)54652</t>
   </si>
   <si>
     <t>PREETHA EVANGELINE D</t>
@@ -7078,7 +7078,7 @@
     <t>Vit54652@123</t>
   </si>
   <si>
-    <t>(multi)54680</t>
+    <t>(MULTI)54680</t>
   </si>
   <si>
     <t>RADHIKA R</t>
@@ -7096,9 +7096,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -7106,36 +7106,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7170,13 +7140,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -7186,22 +7149,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -7213,6 +7168,14 @@
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7231,11 +7194,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7247,7 +7216,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7262,7 +7262,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7274,13 +7340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7292,25 +7358,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7322,127 +7430,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7453,30 +7453,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -7519,17 +7495,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -7548,8 +7513,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7558,148 +7558,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
